--- a/Base de datos.xlsx
+++ b/Base de datos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6f36a482e923c84a/Escritorio/ANGELICA/1. MIS ARCHIVOS/ANGELICA/1. LA CASA DEL SHAMPOO Y ALGO MAS/PROGRAMA SOFTWARE/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cuale\Music\Fer_UANL\9no Semestre\0_Clientes\LaCasaDelShampoo\Software\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{39CC1167-8304-44E8-8676-A537E0E7F27E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42CBC1A5-8282-4719-A036-36FB1B1B1D29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{7D3AD5BD-9129-4109-BA33-DEDC0CCF2DBD}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{7D3AD5BD-9129-4109-BA33-DEDC0CCF2DBD}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="803" uniqueCount="426">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1197" uniqueCount="820">
   <si>
     <t>TIENDA</t>
   </si>
@@ -1317,6 +1317,1188 @@
   </si>
   <si>
     <t>Shampoo neutro</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>P0001</t>
+  </si>
+  <si>
+    <t>P0002</t>
+  </si>
+  <si>
+    <t>P0004</t>
+  </si>
+  <si>
+    <t>P0005</t>
+  </si>
+  <si>
+    <t>P0003</t>
+  </si>
+  <si>
+    <t>P0011</t>
+  </si>
+  <si>
+    <t>P0010</t>
+  </si>
+  <si>
+    <t>P0009</t>
+  </si>
+  <si>
+    <t>P0295</t>
+  </si>
+  <si>
+    <t>P0296</t>
+  </si>
+  <si>
+    <t>P0301</t>
+  </si>
+  <si>
+    <t>P0302</t>
+  </si>
+  <si>
+    <t>P0078</t>
+  </si>
+  <si>
+    <t>P0080</t>
+  </si>
+  <si>
+    <t>P0081</t>
+  </si>
+  <si>
+    <t>P0079</t>
+  </si>
+  <si>
+    <t>P0303</t>
+  </si>
+  <si>
+    <t>P0305</t>
+  </si>
+  <si>
+    <t>P0082</t>
+  </si>
+  <si>
+    <t>P0083</t>
+  </si>
+  <si>
+    <t>P0084</t>
+  </si>
+  <si>
+    <t>P0085</t>
+  </si>
+  <si>
+    <t>P0086</t>
+  </si>
+  <si>
+    <t>P0087</t>
+  </si>
+  <si>
+    <t>P0088</t>
+  </si>
+  <si>
+    <t>P0297</t>
+  </si>
+  <si>
+    <t>P0298</t>
+  </si>
+  <si>
+    <t>P0299</t>
+  </si>
+  <si>
+    <t>P0090</t>
+  </si>
+  <si>
+    <t>P0091</t>
+  </si>
+  <si>
+    <t>P0300</t>
+  </si>
+  <si>
+    <t>P0107</t>
+  </si>
+  <si>
+    <t>P0108</t>
+  </si>
+  <si>
+    <t>P0098</t>
+  </si>
+  <si>
+    <t>P0097</t>
+  </si>
+  <si>
+    <t>P0092</t>
+  </si>
+  <si>
+    <t>P0095</t>
+  </si>
+  <si>
+    <t>P0093</t>
+  </si>
+  <si>
+    <t>P0094</t>
+  </si>
+  <si>
+    <t>P0099</t>
+  </si>
+  <si>
+    <t>P0096</t>
+  </si>
+  <si>
+    <t>P0089</t>
+  </si>
+  <si>
+    <t>P0385</t>
+  </si>
+  <si>
+    <t>P0100</t>
+  </si>
+  <si>
+    <t>P0101</t>
+  </si>
+  <si>
+    <t>P0386</t>
+  </si>
+  <si>
+    <t>P0306</t>
+  </si>
+  <si>
+    <t>P0276</t>
+  </si>
+  <si>
+    <t>P0307</t>
+  </si>
+  <si>
+    <t>P0006</t>
+  </si>
+  <si>
+    <t>P0309</t>
+  </si>
+  <si>
+    <t>P0373</t>
+  </si>
+  <si>
+    <t>P0372</t>
+  </si>
+  <si>
+    <t>P0304</t>
+  </si>
+  <si>
+    <t>P0363</t>
+  </si>
+  <si>
+    <t>P0323</t>
+  </si>
+  <si>
+    <t>P0308</t>
+  </si>
+  <si>
+    <t>P0371</t>
+  </si>
+  <si>
+    <t>P0367</t>
+  </si>
+  <si>
+    <t>P0366</t>
+  </si>
+  <si>
+    <t>P0364</t>
+  </si>
+  <si>
+    <t>P0368</t>
+  </si>
+  <si>
+    <t>P0370</t>
+  </si>
+  <si>
+    <t>P0365</t>
+  </si>
+  <si>
+    <t>P0369</t>
+  </si>
+  <si>
+    <t>P0355</t>
+  </si>
+  <si>
+    <t>P0357</t>
+  </si>
+  <si>
+    <t>P0358</t>
+  </si>
+  <si>
+    <t>P0361</t>
+  </si>
+  <si>
+    <t>P0359</t>
+  </si>
+  <si>
+    <t>P0360</t>
+  </si>
+  <si>
+    <t>P0362</t>
+  </si>
+  <si>
+    <t>P0289</t>
+  </si>
+  <si>
+    <t>P0354</t>
+  </si>
+  <si>
+    <t>P0291</t>
+  </si>
+  <si>
+    <t>P0077</t>
+  </si>
+  <si>
+    <t>P0294</t>
+  </si>
+  <si>
+    <t>P0293</t>
+  </si>
+  <si>
+    <t>P0292</t>
+  </si>
+  <si>
+    <t>P0045</t>
+  </si>
+  <si>
+    <t>P0290</t>
+  </si>
+  <si>
+    <t>P0106</t>
+  </si>
+  <si>
+    <t>P0356</t>
+  </si>
+  <si>
+    <t>P0311</t>
+  </si>
+  <si>
+    <t>P0312</t>
+  </si>
+  <si>
+    <t>P0313</t>
+  </si>
+  <si>
+    <t>P0310</t>
+  </si>
+  <si>
+    <t>P0314</t>
+  </si>
+  <si>
+    <t>P0287</t>
+  </si>
+  <si>
+    <t>P0279</t>
+  </si>
+  <si>
+    <t>P0280</t>
+  </si>
+  <si>
+    <t>P0282</t>
+  </si>
+  <si>
+    <t>P0281</t>
+  </si>
+  <si>
+    <t>P0285</t>
+  </si>
+  <si>
+    <t>P0288</t>
+  </si>
+  <si>
+    <t>P0286</t>
+  </si>
+  <si>
+    <t>P0284</t>
+  </si>
+  <si>
+    <t>P0283</t>
+  </si>
+  <si>
+    <t>P0076</t>
+  </si>
+  <si>
+    <t>P0103</t>
+  </si>
+  <si>
+    <t>P0353</t>
+  </si>
+  <si>
+    <t>P0352</t>
+  </si>
+  <si>
+    <t>P0008</t>
+  </si>
+  <si>
+    <t>P0277</t>
+  </si>
+  <si>
+    <t>P0278</t>
+  </si>
+  <si>
+    <t>P0042</t>
+  </si>
+  <si>
+    <t>P0132</t>
+  </si>
+  <si>
+    <t>P0131</t>
+  </si>
+  <si>
+    <t>P0115</t>
+  </si>
+  <si>
+    <t>P0137</t>
+  </si>
+  <si>
+    <t>P0134</t>
+  </si>
+  <si>
+    <t>P0120</t>
+  </si>
+  <si>
+    <t>P0127</t>
+  </si>
+  <si>
+    <t>P0124</t>
+  </si>
+  <si>
+    <t>P0121</t>
+  </si>
+  <si>
+    <t>P0112</t>
+  </si>
+  <si>
+    <t>P0109</t>
+  </si>
+  <si>
+    <t>P0111</t>
+  </si>
+  <si>
+    <t>P0116</t>
+  </si>
+  <si>
+    <t>P0118</t>
+  </si>
+  <si>
+    <t>P0130</t>
+  </si>
+  <si>
+    <t>P0126</t>
+  </si>
+  <si>
+    <t>P0125</t>
+  </si>
+  <si>
+    <t>P0135</t>
+  </si>
+  <si>
+    <t>P0136</t>
+  </si>
+  <si>
+    <t>P0129</t>
+  </si>
+  <si>
+    <t>P0113</t>
+  </si>
+  <si>
+    <t>P0114</t>
+  </si>
+  <si>
+    <t>P0119</t>
+  </si>
+  <si>
+    <t>P0133</t>
+  </si>
+  <si>
+    <t>P0117</t>
+  </si>
+  <si>
+    <t>P0128</t>
+  </si>
+  <si>
+    <t>P0123</t>
+  </si>
+  <si>
+    <t>P0122</t>
+  </si>
+  <si>
+    <t>P0110</t>
+  </si>
+  <si>
+    <t>P0017</t>
+  </si>
+  <si>
+    <t>P0018</t>
+  </si>
+  <si>
+    <t>P0019</t>
+  </si>
+  <si>
+    <t>P0020</t>
+  </si>
+  <si>
+    <t>P0021</t>
+  </si>
+  <si>
+    <t>P0022</t>
+  </si>
+  <si>
+    <t>P0023</t>
+  </si>
+  <si>
+    <t>P0024</t>
+  </si>
+  <si>
+    <t>P0025</t>
+  </si>
+  <si>
+    <t>P0026</t>
+  </si>
+  <si>
+    <t>P0027</t>
+  </si>
+  <si>
+    <t>P0028</t>
+  </si>
+  <si>
+    <t>P0029</t>
+  </si>
+  <si>
+    <t>P0030</t>
+  </si>
+  <si>
+    <t>P0031</t>
+  </si>
+  <si>
+    <t>P0032</t>
+  </si>
+  <si>
+    <t>P0033</t>
+  </si>
+  <si>
+    <t>P0034</t>
+  </si>
+  <si>
+    <t>P0035</t>
+  </si>
+  <si>
+    <t>P0036</t>
+  </si>
+  <si>
+    <t>P0037</t>
+  </si>
+  <si>
+    <t>P0038</t>
+  </si>
+  <si>
+    <t>P0039</t>
+  </si>
+  <si>
+    <t>P0040</t>
+  </si>
+  <si>
+    <t>P0041</t>
+  </si>
+  <si>
+    <t>P0377</t>
+  </si>
+  <si>
+    <t>P0378</t>
+  </si>
+  <si>
+    <t>P0014</t>
+  </si>
+  <si>
+    <t>P0389</t>
+  </si>
+  <si>
+    <t>P0374</t>
+  </si>
+  <si>
+    <t>P0375</t>
+  </si>
+  <si>
+    <t>P0012</t>
+  </si>
+  <si>
+    <t>P0387</t>
+  </si>
+  <si>
+    <t>P0376</t>
+  </si>
+  <si>
+    <t>P0013</t>
+  </si>
+  <si>
+    <t>P0388</t>
+  </si>
+  <si>
+    <t>P0007</t>
+  </si>
+  <si>
+    <t>P0315</t>
+  </si>
+  <si>
+    <t>P0380</t>
+  </si>
+  <si>
+    <t>P0379</t>
+  </si>
+  <si>
+    <t>P0015</t>
+  </si>
+  <si>
+    <t>P0390</t>
+  </si>
+  <si>
+    <t>P0324</t>
+  </si>
+  <si>
+    <t>P0325</t>
+  </si>
+  <si>
+    <t>P0326</t>
+  </si>
+  <si>
+    <t>P0327</t>
+  </si>
+  <si>
+    <t>P0328</t>
+  </si>
+  <si>
+    <t>P0329</t>
+  </si>
+  <si>
+    <t>P0330</t>
+  </si>
+  <si>
+    <t>P0331</t>
+  </si>
+  <si>
+    <t>P0332</t>
+  </si>
+  <si>
+    <t>P0333</t>
+  </si>
+  <si>
+    <t>P0334</t>
+  </si>
+  <si>
+    <t>P0335</t>
+  </si>
+  <si>
+    <t>P0336</t>
+  </si>
+  <si>
+    <t>P0337</t>
+  </si>
+  <si>
+    <t>P0338</t>
+  </si>
+  <si>
+    <t>P0339</t>
+  </si>
+  <si>
+    <t>P0340</t>
+  </si>
+  <si>
+    <t>P0341</t>
+  </si>
+  <si>
+    <t>P0342</t>
+  </si>
+  <si>
+    <t>P0346</t>
+  </si>
+  <si>
+    <t>P0347</t>
+  </si>
+  <si>
+    <t>P0348</t>
+  </si>
+  <si>
+    <t>P0349</t>
+  </si>
+  <si>
+    <t>P0350</t>
+  </si>
+  <si>
+    <t>P0351</t>
+  </si>
+  <si>
+    <t>P0343</t>
+  </si>
+  <si>
+    <t>P0344</t>
+  </si>
+  <si>
+    <t>P0345</t>
+  </si>
+  <si>
+    <t>P0322</t>
+  </si>
+  <si>
+    <t>P0320</t>
+  </si>
+  <si>
+    <t>P0321</t>
+  </si>
+  <si>
+    <t>P0147</t>
+  </si>
+  <si>
+    <t>P0139</t>
+  </si>
+  <si>
+    <t>P0144</t>
+  </si>
+  <si>
+    <t>P0145</t>
+  </si>
+  <si>
+    <t>P0140</t>
+  </si>
+  <si>
+    <t>P0142</t>
+  </si>
+  <si>
+    <t>P0148</t>
+  </si>
+  <si>
+    <t>P0146</t>
+  </si>
+  <si>
+    <t>P0143</t>
+  </si>
+  <si>
+    <t>P0141</t>
+  </si>
+  <si>
+    <t>P0182</t>
+  </si>
+  <si>
+    <t>P0184</t>
+  </si>
+  <si>
+    <t>P0183</t>
+  </si>
+  <si>
+    <t>P0185</t>
+  </si>
+  <si>
+    <t>P0186</t>
+  </si>
+  <si>
+    <t>P0187</t>
+  </si>
+  <si>
+    <t>P0188</t>
+  </si>
+  <si>
+    <t>P0104</t>
+  </si>
+  <si>
+    <t>P0189</t>
+  </si>
+  <si>
+    <t>P0190</t>
+  </si>
+  <si>
+    <t>P0191</t>
+  </si>
+  <si>
+    <t>P0192</t>
+  </si>
+  <si>
+    <t>P0193</t>
+  </si>
+  <si>
+    <t>P0194</t>
+  </si>
+  <si>
+    <t>P0196</t>
+  </si>
+  <si>
+    <t>P0198</t>
+  </si>
+  <si>
+    <t>P0197</t>
+  </si>
+  <si>
+    <t>P0195</t>
+  </si>
+  <si>
+    <t>P0199</t>
+  </si>
+  <si>
+    <t>P0200</t>
+  </si>
+  <si>
+    <t>P0201</t>
+  </si>
+  <si>
+    <t>P0202</t>
+  </si>
+  <si>
+    <t>P0154</t>
+  </si>
+  <si>
+    <t>P0155</t>
+  </si>
+  <si>
+    <t>P0156</t>
+  </si>
+  <si>
+    <t>P0157</t>
+  </si>
+  <si>
+    <t>P0158</t>
+  </si>
+  <si>
+    <t>P0159</t>
+  </si>
+  <si>
+    <t>P0160</t>
+  </si>
+  <si>
+    <t>P0161</t>
+  </si>
+  <si>
+    <t>P0162</t>
+  </si>
+  <si>
+    <t>P0163</t>
+  </si>
+  <si>
+    <t>P0164</t>
+  </si>
+  <si>
+    <t>P0165</t>
+  </si>
+  <si>
+    <t>P0166</t>
+  </si>
+  <si>
+    <t>P0167</t>
+  </si>
+  <si>
+    <t>P0168</t>
+  </si>
+  <si>
+    <t>P0169</t>
+  </si>
+  <si>
+    <t>P0170</t>
+  </si>
+  <si>
+    <t>P0171</t>
+  </si>
+  <si>
+    <t>P0181</t>
+  </si>
+  <si>
+    <t>P0172</t>
+  </si>
+  <si>
+    <t>P0174</t>
+  </si>
+  <si>
+    <t>P0173</t>
+  </si>
+  <si>
+    <t>P0175</t>
+  </si>
+  <si>
+    <t>P0176</t>
+  </si>
+  <si>
+    <t>P0177</t>
+  </si>
+  <si>
+    <t>P0178</t>
+  </si>
+  <si>
+    <t>P0179</t>
+  </si>
+  <si>
+    <t>P0180</t>
+  </si>
+  <si>
+    <t>P0211</t>
+  </si>
+  <si>
+    <t>P0207</t>
+  </si>
+  <si>
+    <t>P0209</t>
+  </si>
+  <si>
+    <t>P0212</t>
+  </si>
+  <si>
+    <t>P0214</t>
+  </si>
+  <si>
+    <t>P0213</t>
+  </si>
+  <si>
+    <t>P0208</t>
+  </si>
+  <si>
+    <t>P0210</t>
+  </si>
+  <si>
+    <t>P0105</t>
+  </si>
+  <si>
+    <t>P0222</t>
+  </si>
+  <si>
+    <t>P0225</t>
+  </si>
+  <si>
+    <t>P0223</t>
+  </si>
+  <si>
+    <t>P0220</t>
+  </si>
+  <si>
+    <t>P0221</t>
+  </si>
+  <si>
+    <t>P0219</t>
+  </si>
+  <si>
+    <t>P0224</t>
+  </si>
+  <si>
+    <t>P0203</t>
+  </si>
+  <si>
+    <t>P0205</t>
+  </si>
+  <si>
+    <t>P0206</t>
+  </si>
+  <si>
+    <t>P0204</t>
+  </si>
+  <si>
+    <t>P0152</t>
+  </si>
+  <si>
+    <t>P0150</t>
+  </si>
+  <si>
+    <t>P0151</t>
+  </si>
+  <si>
+    <t>P0149</t>
+  </si>
+  <si>
+    <t>P0153</t>
+  </si>
+  <si>
+    <t>P0226</t>
+  </si>
+  <si>
+    <t>P0227</t>
+  </si>
+  <si>
+    <t>P0228</t>
+  </si>
+  <si>
+    <t>P0043</t>
+  </si>
+  <si>
+    <t>P0044</t>
+  </si>
+  <si>
+    <t>P0229</t>
+  </si>
+  <si>
+    <t>P0230</t>
+  </si>
+  <si>
+    <t>P0231</t>
+  </si>
+  <si>
+    <t>P0232</t>
+  </si>
+  <si>
+    <t>P0233</t>
+  </si>
+  <si>
+    <t>P0234</t>
+  </si>
+  <si>
+    <t>P0235</t>
+  </si>
+  <si>
+    <t>P0236</t>
+  </si>
+  <si>
+    <t>P0237</t>
+  </si>
+  <si>
+    <t>P0238</t>
+  </si>
+  <si>
+    <t>P0239</t>
+  </si>
+  <si>
+    <t>P0240</t>
+  </si>
+  <si>
+    <t>P0241</t>
+  </si>
+  <si>
+    <t>P0242</t>
+  </si>
+  <si>
+    <t>P0243</t>
+  </si>
+  <si>
+    <t>P0244</t>
+  </si>
+  <si>
+    <t>P0245</t>
+  </si>
+  <si>
+    <t>P0246</t>
+  </si>
+  <si>
+    <t>P0247</t>
+  </si>
+  <si>
+    <t>P0248</t>
+  </si>
+  <si>
+    <t>P0249</t>
+  </si>
+  <si>
+    <t>P0250</t>
+  </si>
+  <si>
+    <t>P0251</t>
+  </si>
+  <si>
+    <t>P0252</t>
+  </si>
+  <si>
+    <t>P0265</t>
+  </si>
+  <si>
+    <t>P0266</t>
+  </si>
+  <si>
+    <t>P0267</t>
+  </si>
+  <si>
+    <t>P0268</t>
+  </si>
+  <si>
+    <t>P0269</t>
+  </si>
+  <si>
+    <t>P0270</t>
+  </si>
+  <si>
+    <t>P0271</t>
+  </si>
+  <si>
+    <t>P0272</t>
+  </si>
+  <si>
+    <t>P0273</t>
+  </si>
+  <si>
+    <t>P0274</t>
+  </si>
+  <si>
+    <t>P0275</t>
+  </si>
+  <si>
+    <t>P0138</t>
+  </si>
+  <si>
+    <t>P0253</t>
+  </si>
+  <si>
+    <t>P0254</t>
+  </si>
+  <si>
+    <t>P0255</t>
+  </si>
+  <si>
+    <t>P0256</t>
+  </si>
+  <si>
+    <t>P0257</t>
+  </si>
+  <si>
+    <t>P0258</t>
+  </si>
+  <si>
+    <t>P0259</t>
+  </si>
+  <si>
+    <t>P0260</t>
+  </si>
+  <si>
+    <t>P0261</t>
+  </si>
+  <si>
+    <t>P0264</t>
+  </si>
+  <si>
+    <t>P0262</t>
+  </si>
+  <si>
+    <t>P0263</t>
+  </si>
+  <si>
+    <t>P0217</t>
+  </si>
+  <si>
+    <t>P0216</t>
+  </si>
+  <si>
+    <t>P0215</t>
+  </si>
+  <si>
+    <t>P0218</t>
+  </si>
+  <si>
+    <t>P0316</t>
+  </si>
+  <si>
+    <t>P0381</t>
+  </si>
+  <si>
+    <t>P0391</t>
+  </si>
+  <si>
+    <t>P0382</t>
+  </si>
+  <si>
+    <t>P0317</t>
+  </si>
+  <si>
+    <t>P0392</t>
+  </si>
+  <si>
+    <t>P0318</t>
+  </si>
+  <si>
+    <t>P0383</t>
+  </si>
+  <si>
+    <t>P0016</t>
+  </si>
+  <si>
+    <t>P0102</t>
+  </si>
+  <si>
+    <t>P0319</t>
+  </si>
+  <si>
+    <t>P0384</t>
+  </si>
+  <si>
+    <t>P0047</t>
+  </si>
+  <si>
+    <t>P0048</t>
+  </si>
+  <si>
+    <t>P0049</t>
+  </si>
+  <si>
+    <t>P0050</t>
+  </si>
+  <si>
+    <t>P0051</t>
+  </si>
+  <si>
+    <t>P0052</t>
+  </si>
+  <si>
+    <t>P0053</t>
+  </si>
+  <si>
+    <t>P0054</t>
+  </si>
+  <si>
+    <t>P0055</t>
+  </si>
+  <si>
+    <t>P0057</t>
+  </si>
+  <si>
+    <t>P0056</t>
+  </si>
+  <si>
+    <t>P0058</t>
+  </si>
+  <si>
+    <t>P0059</t>
+  </si>
+  <si>
+    <t>P0061</t>
+  </si>
+  <si>
+    <t>P0062</t>
+  </si>
+  <si>
+    <t>P0060</t>
+  </si>
+  <si>
+    <t>P0066</t>
+  </si>
+  <si>
+    <t>P0064</t>
+  </si>
+  <si>
+    <t>P0065</t>
+  </si>
+  <si>
+    <t>P0063</t>
+  </si>
+  <si>
+    <t>P0075</t>
+  </si>
+  <si>
+    <t>P0069</t>
+  </si>
+  <si>
+    <t>P0073</t>
+  </si>
+  <si>
+    <t>P0074</t>
+  </si>
+  <si>
+    <t>P0068</t>
+  </si>
+  <si>
+    <t>P0072</t>
+  </si>
+  <si>
+    <t>P0071</t>
+  </si>
+  <si>
+    <t>P0067</t>
+  </si>
+  <si>
+    <t>P0070</t>
+  </si>
+  <si>
+    <t>P0046</t>
+  </si>
+  <si>
+    <t>CÓDIGO DE BARRA</t>
   </si>
 </sst>
 </file>
@@ -1327,7 +2509,7 @@
     <numFmt numFmtId="44" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_-[$$-80A]* #,##0.00_-;\-[$$-80A]* #,##0.00_-;_-[$$-80A]* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1366,6 +2548,18 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="48"/>
+      <color theme="1"/>
+      <name val="Libre Barcode 39"/>
     </font>
   </fonts>
   <fills count="15">
@@ -1495,7 +2689,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1600,9 +2794,14 @@
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Moneda" xfId="1" builtinId="4"/>
+    <cellStyle name="Currency" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1619,7 +2818,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1935,8 +3134,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1872F13F-1F6D-4952-99B1-66C80450CFA2}">
-  <dimension ref="A1:J393"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:L393"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.28515625" style="40" customWidth="1"/>
     <col min="2" max="2" width="13.28515625" style="40" bestFit="1" customWidth="1"/>
@@ -1947,9 +3146,11 @@
     <col min="7" max="7" width="11.42578125" style="41"/>
     <col min="8" max="9" width="15.28515625" style="41" customWidth="1"/>
     <col min="10" max="10" width="11.42578125" style="41"/>
+    <col min="11" max="11" width="11.42578125" style="42"/>
+    <col min="12" max="12" width="62.7109375" style="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" ht="30.75" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1980,8 +3181,14 @@
       <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K1" s="42" t="s">
+        <v>426</v>
+      </c>
+      <c r="L1" s="43" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>10</v>
       </c>
@@ -2012,8 +3219,15 @@
       <c r="J2" s="10">
         <v>200</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K2" s="42" t="s">
+        <v>427</v>
+      </c>
+      <c r="L2" s="44" t="str">
+        <f t="shared" ref="L2:L65" si="0">"*"&amp;UPPER(K2)&amp;"*"</f>
+        <v>*P0001*</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>15</v>
       </c>
@@ -2044,8 +3258,15 @@
       <c r="J3" s="10">
         <v>200</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K3" s="42" t="s">
+        <v>428</v>
+      </c>
+      <c r="L3" s="44" t="str">
+        <f t="shared" si="0"/>
+        <v>*P0002*</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>22</v>
       </c>
@@ -2074,8 +3295,15 @@
       <c r="J4" s="10">
         <v>250</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K4" s="42" t="s">
+        <v>429</v>
+      </c>
+      <c r="L4" s="44" t="str">
+        <f t="shared" si="0"/>
+        <v>*P0004*</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6"/>
       <c r="B5" s="6"/>
       <c r="C5" s="7" t="s">
@@ -2100,8 +3328,15 @@
       <c r="J5" s="10">
         <v>200</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K5" s="42" t="s">
+        <v>430</v>
+      </c>
+      <c r="L5" s="44" t="str">
+        <f t="shared" si="0"/>
+        <v>*P0005*</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6"/>
       <c r="B6" s="6"/>
       <c r="C6" s="7" t="s">
@@ -2126,8 +3361,15 @@
       <c r="J6" s="10">
         <v>200</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K6" s="42" t="s">
+        <v>431</v>
+      </c>
+      <c r="L6" s="44" t="str">
+        <f t="shared" si="0"/>
+        <v>*P0003*</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="6"/>
       <c r="B7" s="6"/>
       <c r="C7" s="12" t="s">
@@ -2152,8 +3394,15 @@
       <c r="J7" s="15">
         <v>235</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K7" s="42" t="s">
+        <v>432</v>
+      </c>
+      <c r="L7" s="44" t="str">
+        <f t="shared" si="0"/>
+        <v>*P0011*</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6"/>
       <c r="B8" s="6"/>
       <c r="C8" s="7" t="s">
@@ -2178,8 +3427,15 @@
       <c r="J8" s="10">
         <v>235</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K8" s="42" t="s">
+        <v>433</v>
+      </c>
+      <c r="L8" s="44" t="str">
+        <f t="shared" si="0"/>
+        <v>*P0010*</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6"/>
       <c r="B9" s="6"/>
       <c r="C9" s="7" t="s">
@@ -2204,8 +3460,15 @@
       <c r="J9" s="10">
         <v>180</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K9" s="42" t="s">
+        <v>434</v>
+      </c>
+      <c r="L9" s="44" t="str">
+        <f t="shared" si="0"/>
+        <v>*P0009*</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="6"/>
       <c r="B10" s="6"/>
       <c r="C10" s="7" t="s">
@@ -2230,8 +3493,15 @@
       <c r="J10" s="10">
         <v>120</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K10" s="42" t="s">
+        <v>435</v>
+      </c>
+      <c r="L10" s="44" t="str">
+        <f t="shared" si="0"/>
+        <v>*P0295*</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="6"/>
       <c r="B11" s="6"/>
       <c r="C11" s="7" t="s">
@@ -2256,8 +3526,15 @@
       <c r="J11" s="10">
         <v>120</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K11" s="42" t="s">
+        <v>436</v>
+      </c>
+      <c r="L11" s="44" t="str">
+        <f t="shared" si="0"/>
+        <v>*P0296*</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6"/>
       <c r="B12" s="6"/>
       <c r="C12" s="12" t="s">
@@ -2282,8 +3559,15 @@
       <c r="J12" s="10">
         <v>200</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K12" s="42" t="s">
+        <v>437</v>
+      </c>
+      <c r="L12" s="44" t="str">
+        <f t="shared" si="0"/>
+        <v>*P0301*</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="6"/>
       <c r="B13" s="6"/>
       <c r="C13" s="12" t="s">
@@ -2308,8 +3592,15 @@
       <c r="J13" s="15">
         <v>200</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K13" s="42" t="s">
+        <v>438</v>
+      </c>
+      <c r="L13" s="44" t="str">
+        <f t="shared" si="0"/>
+        <v>*P0302*</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="6"/>
       <c r="B14" s="6"/>
       <c r="C14" s="7" t="s">
@@ -2334,8 +3625,15 @@
       <c r="J14" s="10">
         <v>200</v>
       </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K14" s="42" t="s">
+        <v>439</v>
+      </c>
+      <c r="L14" s="44" t="str">
+        <f t="shared" si="0"/>
+        <v>*P0078*</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="6"/>
       <c r="B15" s="6"/>
       <c r="C15" s="7" t="s">
@@ -2360,8 +3658,15 @@
       <c r="J15" s="10">
         <v>220</v>
       </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K15" s="42" t="s">
+        <v>440</v>
+      </c>
+      <c r="L15" s="44" t="str">
+        <f t="shared" si="0"/>
+        <v>*P0080*</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6"/>
       <c r="B16" s="6"/>
       <c r="C16" s="7" t="s">
@@ -2386,8 +3691,15 @@
       <c r="J16" s="10">
         <v>250</v>
       </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K16" s="42" t="s">
+        <v>441</v>
+      </c>
+      <c r="L16" s="44" t="str">
+        <f t="shared" si="0"/>
+        <v>*P0081*</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="6"/>
       <c r="B17" s="6"/>
       <c r="C17" s="7" t="s">
@@ -2412,8 +3724,15 @@
       <c r="J17" s="10">
         <v>220</v>
       </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K17" s="42" t="s">
+        <v>442</v>
+      </c>
+      <c r="L17" s="44" t="str">
+        <f t="shared" si="0"/>
+        <v>*P0079*</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6"/>
       <c r="B18" s="6"/>
       <c r="C18" s="12" t="s">
@@ -2438,8 +3757,15 @@
       <c r="J18" s="10">
         <v>130</v>
       </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K18" s="42" t="s">
+        <v>443</v>
+      </c>
+      <c r="L18" s="44" t="str">
+        <f t="shared" si="0"/>
+        <v>*P0303*</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="6"/>
       <c r="B19" s="6"/>
       <c r="C19" s="12" t="s">
@@ -2464,8 +3790,15 @@
       <c r="J19" s="10">
         <v>265</v>
       </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K19" s="42" t="s">
+        <v>444</v>
+      </c>
+      <c r="L19" s="44" t="str">
+        <f t="shared" si="0"/>
+        <v>*P0305*</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6"/>
       <c r="B20" s="6"/>
       <c r="C20" s="7" t="s">
@@ -2490,8 +3823,15 @@
       <c r="J20" s="10">
         <v>350</v>
       </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K20" s="42" t="s">
+        <v>445</v>
+      </c>
+      <c r="L20" s="44" t="str">
+        <f t="shared" si="0"/>
+        <v>*P0082*</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6"/>
       <c r="B21" s="6"/>
       <c r="C21" s="7" t="s">
@@ -2516,8 +3856,15 @@
       <c r="J21" s="10">
         <v>350</v>
       </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K21" s="42" t="s">
+        <v>446</v>
+      </c>
+      <c r="L21" s="44" t="str">
+        <f t="shared" si="0"/>
+        <v>*P0083*</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6"/>
       <c r="B22" s="6"/>
       <c r="C22" s="7" t="s">
@@ -2542,8 +3889,15 @@
       <c r="J22" s="10">
         <v>220</v>
       </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K22" s="42" t="s">
+        <v>447</v>
+      </c>
+      <c r="L22" s="44" t="str">
+        <f t="shared" si="0"/>
+        <v>*P0084*</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="6"/>
       <c r="B23" s="6"/>
       <c r="C23" s="7" t="s">
@@ -2568,8 +3922,15 @@
       <c r="J23" s="10">
         <v>250</v>
       </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K23" s="42" t="s">
+        <v>448</v>
+      </c>
+      <c r="L23" s="44" t="str">
+        <f t="shared" si="0"/>
+        <v>*P0085*</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6"/>
       <c r="B24" s="6"/>
       <c r="C24" s="12" t="s">
@@ -2594,8 +3955,15 @@
       <c r="J24" s="15">
         <v>350</v>
       </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K24" s="42" t="s">
+        <v>449</v>
+      </c>
+      <c r="L24" s="44" t="str">
+        <f t="shared" si="0"/>
+        <v>*P0086*</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="6"/>
       <c r="B25" s="6"/>
       <c r="C25" s="7" t="s">
@@ -2620,8 +3988,15 @@
       <c r="J25" s="10">
         <v>220</v>
       </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K25" s="42" t="s">
+        <v>450</v>
+      </c>
+      <c r="L25" s="44" t="str">
+        <f t="shared" si="0"/>
+        <v>*P0087*</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6"/>
       <c r="B26" s="6"/>
       <c r="C26" s="7" t="s">
@@ -2646,8 +4021,15 @@
       <c r="J26" s="10">
         <v>95</v>
       </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K26" s="42" t="s">
+        <v>451</v>
+      </c>
+      <c r="L26" s="44" t="str">
+        <f t="shared" si="0"/>
+        <v>*P0088*</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="6"/>
       <c r="B27" s="6"/>
       <c r="C27" s="7" t="s">
@@ -2672,8 +4054,15 @@
       <c r="J27" s="10">
         <v>190</v>
       </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K27" s="42" t="s">
+        <v>452</v>
+      </c>
+      <c r="L27" s="44" t="str">
+        <f t="shared" si="0"/>
+        <v>*P0297*</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="6"/>
       <c r="B28" s="6"/>
       <c r="C28" s="7" t="s">
@@ -2698,8 +4087,15 @@
       <c r="J28" s="10">
         <v>300</v>
       </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K28" s="42" t="s">
+        <v>453</v>
+      </c>
+      <c r="L28" s="44" t="str">
+        <f t="shared" si="0"/>
+        <v>*P0298*</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="6"/>
       <c r="B29" s="6"/>
       <c r="C29" s="7" t="s">
@@ -2724,8 +4120,15 @@
       <c r="J29" s="10">
         <v>200</v>
       </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K29" s="42" t="s">
+        <v>454</v>
+      </c>
+      <c r="L29" s="44" t="str">
+        <f t="shared" si="0"/>
+        <v>*P0299*</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="6"/>
       <c r="B30" s="6"/>
       <c r="C30" s="7" t="s">
@@ -2750,8 +4153,15 @@
       <c r="J30" s="10">
         <v>210</v>
       </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K30" s="42" t="s">
+        <v>455</v>
+      </c>
+      <c r="L30" s="44" t="str">
+        <f t="shared" si="0"/>
+        <v>*P0090*</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="6"/>
       <c r="B31" s="6"/>
       <c r="C31" s="7" t="s">
@@ -2776,8 +4186,15 @@
       <c r="J31" s="10">
         <v>200</v>
       </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K31" s="42" t="s">
+        <v>456</v>
+      </c>
+      <c r="L31" s="44" t="str">
+        <f t="shared" si="0"/>
+        <v>*P0091*</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="6"/>
       <c r="B32" s="6"/>
       <c r="C32" s="7" t="s">
@@ -2802,8 +4219,15 @@
       <c r="J32" s="10">
         <v>220</v>
       </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K32" s="42" t="s">
+        <v>457</v>
+      </c>
+      <c r="L32" s="44" t="str">
+        <f t="shared" si="0"/>
+        <v>*P0300*</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="6"/>
       <c r="B33" s="6"/>
       <c r="C33" s="7" t="s">
@@ -2828,8 +4252,15 @@
       <c r="J33" s="10">
         <v>140</v>
       </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K33" s="42" t="s">
+        <v>458</v>
+      </c>
+      <c r="L33" s="44" t="str">
+        <f t="shared" si="0"/>
+        <v>*P0107*</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="6"/>
       <c r="B34" s="6"/>
       <c r="C34" s="7" t="s">
@@ -2854,8 +4285,15 @@
       <c r="J34" s="10">
         <v>250</v>
       </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K34" s="42" t="s">
+        <v>459</v>
+      </c>
+      <c r="L34" s="44" t="str">
+        <f t="shared" si="0"/>
+        <v>*P0108*</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="6"/>
       <c r="B35" s="6"/>
       <c r="C35" s="7" t="s">
@@ -2880,8 +4318,15 @@
       <c r="J35" s="10">
         <v>100</v>
       </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K35" s="42" t="s">
+        <v>460</v>
+      </c>
+      <c r="L35" s="44" t="str">
+        <f t="shared" si="0"/>
+        <v>*P0098*</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="6"/>
       <c r="B36" s="6"/>
       <c r="C36" s="7" t="s">
@@ -2904,8 +4349,15 @@
       <c r="J36" s="10">
         <v>100</v>
       </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K36" s="42" t="s">
+        <v>461</v>
+      </c>
+      <c r="L36" s="44" t="str">
+        <f t="shared" si="0"/>
+        <v>*P0097*</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="6"/>
       <c r="B37" s="6"/>
       <c r="C37" s="7" t="s">
@@ -2928,8 +4380,15 @@
       <c r="J37" s="10">
         <v>160</v>
       </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K37" s="42" t="s">
+        <v>462</v>
+      </c>
+      <c r="L37" s="44" t="str">
+        <f t="shared" si="0"/>
+        <v>*P0092*</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="6"/>
       <c r="B38" s="6"/>
       <c r="C38" s="7" t="s">
@@ -2952,8 +4411,15 @@
       <c r="J38" s="10">
         <v>100</v>
       </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K38" s="42" t="s">
+        <v>463</v>
+      </c>
+      <c r="L38" s="44" t="str">
+        <f t="shared" si="0"/>
+        <v>*P0095*</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="6"/>
       <c r="B39" s="6"/>
       <c r="C39" s="7" t="s">
@@ -2978,8 +4444,15 @@
       <c r="J39" s="10">
         <v>180</v>
       </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K39" s="42" t="s">
+        <v>464</v>
+      </c>
+      <c r="L39" s="44" t="str">
+        <f t="shared" si="0"/>
+        <v>*P0093*</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="6"/>
       <c r="B40" s="6"/>
       <c r="C40" s="7" t="s">
@@ -3004,8 +4477,15 @@
       <c r="J40" s="10">
         <v>160</v>
       </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K40" s="42" t="s">
+        <v>465</v>
+      </c>
+      <c r="L40" s="44" t="str">
+        <f t="shared" si="0"/>
+        <v>*P0094*</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="6"/>
       <c r="B41" s="6"/>
       <c r="C41" s="12" t="s">
@@ -3030,8 +4510,15 @@
       <c r="J41" s="15">
         <v>160</v>
       </c>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K41" s="42" t="s">
+        <v>466</v>
+      </c>
+      <c r="L41" s="44" t="str">
+        <f t="shared" si="0"/>
+        <v>*P0099*</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="6"/>
       <c r="B42" s="6"/>
       <c r="C42" s="7" t="s">
@@ -3056,8 +4543,15 @@
       <c r="J42" s="10">
         <v>180</v>
       </c>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K42" s="42" t="s">
+        <v>467</v>
+      </c>
+      <c r="L42" s="44" t="str">
+        <f t="shared" si="0"/>
+        <v>*P0096*</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="6"/>
       <c r="B43" s="6"/>
       <c r="C43" s="7" t="s">
@@ -3082,8 +4576,15 @@
       <c r="J43" s="10">
         <v>240</v>
       </c>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K43" s="42" t="s">
+        <v>468</v>
+      </c>
+      <c r="L43" s="44" t="str">
+        <f t="shared" si="0"/>
+        <v>*P0089*</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="6"/>
       <c r="B44" s="6"/>
       <c r="C44" s="12" t="s">
@@ -3108,8 +4609,15 @@
       <c r="J44" s="15">
         <v>235</v>
       </c>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K44" s="42" t="s">
+        <v>469</v>
+      </c>
+      <c r="L44" s="44" t="str">
+        <f t="shared" si="0"/>
+        <v>*P0385*</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="6"/>
       <c r="B45" s="6"/>
       <c r="C45" s="7" t="s">
@@ -3134,8 +4642,15 @@
       <c r="J45" s="10">
         <v>250</v>
       </c>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K45" s="42" t="s">
+        <v>470</v>
+      </c>
+      <c r="L45" s="44" t="str">
+        <f t="shared" si="0"/>
+        <v>*P0100*</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="6"/>
       <c r="B46" s="6"/>
       <c r="C46" s="7" t="s">
@@ -3160,8 +4675,15 @@
       <c r="J46" s="10">
         <v>220</v>
       </c>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K46" s="42" t="s">
+        <v>471</v>
+      </c>
+      <c r="L46" s="44" t="str">
+        <f t="shared" si="0"/>
+        <v>*P0101*</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="6"/>
       <c r="B47" s="6"/>
       <c r="C47" s="7" t="s">
@@ -3186,8 +4708,15 @@
       <c r="J47" s="10">
         <v>265</v>
       </c>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K47" s="42" t="s">
+        <v>472</v>
+      </c>
+      <c r="L47" s="44" t="str">
+        <f t="shared" si="0"/>
+        <v>*P0386*</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="6"/>
       <c r="B48" s="6"/>
       <c r="C48" s="7" t="s">
@@ -3212,8 +4741,15 @@
       <c r="J48" s="10">
         <v>300</v>
       </c>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K48" s="42" t="s">
+        <v>473</v>
+      </c>
+      <c r="L48" s="44" t="str">
+        <f t="shared" si="0"/>
+        <v>*P0306*</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="6"/>
       <c r="B49" s="6"/>
       <c r="C49" s="7" t="s">
@@ -3238,8 +4774,15 @@
       <c r="J49" s="10">
         <v>200</v>
       </c>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K49" s="42" t="s">
+        <v>474</v>
+      </c>
+      <c r="L49" s="44" t="str">
+        <f t="shared" si="0"/>
+        <v>*P0276*</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="6"/>
       <c r="B50" s="6"/>
       <c r="C50" s="7" t="s">
@@ -3264,8 +4807,15 @@
       <c r="J50" s="10">
         <v>220</v>
       </c>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K50" s="42" t="s">
+        <v>475</v>
+      </c>
+      <c r="L50" s="44" t="str">
+        <f t="shared" si="0"/>
+        <v>*P0307*</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="6"/>
       <c r="B51" s="6"/>
       <c r="C51" s="7" t="s">
@@ -3290,8 +4840,15 @@
       <c r="J51" s="10">
         <v>260</v>
       </c>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K51" s="42" t="s">
+        <v>476</v>
+      </c>
+      <c r="L51" s="44" t="str">
+        <f t="shared" si="0"/>
+        <v>*P0006*</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="6"/>
       <c r="B52" s="6"/>
       <c r="C52" s="12" t="s">
@@ -3316,8 +4873,15 @@
       <c r="J52" s="15">
         <v>250</v>
       </c>
-    </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K52" s="42" t="s">
+        <v>477</v>
+      </c>
+      <c r="L52" s="44" t="str">
+        <f t="shared" si="0"/>
+        <v>*P0309*</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="6"/>
       <c r="B53" s="6"/>
       <c r="C53" s="7" t="s">
@@ -3342,8 +4906,15 @@
       <c r="J53" s="10">
         <v>235</v>
       </c>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K53" s="42" t="s">
+        <v>478</v>
+      </c>
+      <c r="L53" s="44" t="str">
+        <f t="shared" si="0"/>
+        <v>*P0373*</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="6"/>
       <c r="B54" s="6"/>
       <c r="C54" s="7" t="s">
@@ -3368,8 +4939,15 @@
       <c r="J54" s="10">
         <v>220</v>
       </c>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K54" s="42" t="s">
+        <v>479</v>
+      </c>
+      <c r="L54" s="44" t="str">
+        <f t="shared" si="0"/>
+        <v>*P0372*</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="6"/>
       <c r="B55" s="6"/>
       <c r="C55" s="12" t="s">
@@ -3394,8 +4972,15 @@
       <c r="J55" s="15">
         <v>235</v>
       </c>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K55" s="42" t="s">
+        <v>480</v>
+      </c>
+      <c r="L55" s="44" t="str">
+        <f t="shared" si="0"/>
+        <v>*P0304*</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="6"/>
       <c r="B56" s="6"/>
       <c r="C56" s="7" t="s">
@@ -3416,8 +5001,15 @@
       <c r="J56" s="10">
         <v>180</v>
       </c>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K56" s="42" t="s">
+        <v>481</v>
+      </c>
+      <c r="L56" s="44" t="str">
+        <f t="shared" si="0"/>
+        <v>*P0363*</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="6"/>
       <c r="B57" s="6"/>
       <c r="C57" s="12" t="s">
@@ -3442,8 +5034,15 @@
       <c r="J57" s="15">
         <v>350</v>
       </c>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K57" s="42" t="s">
+        <v>482</v>
+      </c>
+      <c r="L57" s="44" t="str">
+        <f t="shared" si="0"/>
+        <v>*P0323*</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="6"/>
       <c r="B58" s="6"/>
       <c r="C58" s="7" t="s">
@@ -3468,8 +5067,15 @@
       <c r="J58" s="10">
         <v>350</v>
       </c>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K58" s="42" t="s">
+        <v>483</v>
+      </c>
+      <c r="L58" s="44" t="str">
+        <f t="shared" si="0"/>
+        <v>*P0308*</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="6"/>
       <c r="B59" s="6"/>
       <c r="C59" s="7" t="s">
@@ -3494,8 +5100,15 @@
       <c r="J59" s="10">
         <v>180</v>
       </c>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K59" s="42" t="s">
+        <v>484</v>
+      </c>
+      <c r="L59" s="44" t="str">
+        <f t="shared" si="0"/>
+        <v>*P0371*</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="6"/>
       <c r="B60" s="6"/>
       <c r="C60" s="7" t="s">
@@ -3520,8 +5133,15 @@
       <c r="J60" s="10">
         <v>180</v>
       </c>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K60" s="42" t="s">
+        <v>485</v>
+      </c>
+      <c r="L60" s="44" t="str">
+        <f t="shared" si="0"/>
+        <v>*P0367*</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="6"/>
       <c r="B61" s="6"/>
       <c r="C61" s="7" t="s">
@@ -3546,8 +5166,15 @@
       <c r="J61" s="10">
         <v>180</v>
       </c>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K61" s="42" t="s">
+        <v>486</v>
+      </c>
+      <c r="L61" s="44" t="str">
+        <f t="shared" si="0"/>
+        <v>*P0366*</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="6"/>
       <c r="B62" s="6"/>
       <c r="C62" s="12" t="s">
@@ -3572,8 +5199,15 @@
       <c r="J62" s="15">
         <v>250</v>
       </c>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K62" s="42" t="s">
+        <v>487</v>
+      </c>
+      <c r="L62" s="44" t="str">
+        <f t="shared" si="0"/>
+        <v>*P0364*</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="6"/>
       <c r="B63" s="6"/>
       <c r="C63" s="7" t="s">
@@ -3598,8 +5232,15 @@
       <c r="J63" s="10">
         <v>180</v>
       </c>
-    </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K63" s="42" t="s">
+        <v>488</v>
+      </c>
+      <c r="L63" s="44" t="str">
+        <f t="shared" si="0"/>
+        <v>*P0368*</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="6"/>
       <c r="B64" s="6"/>
       <c r="C64" s="7" t="s">
@@ -3624,8 +5265,15 @@
       <c r="J64" s="10">
         <v>180</v>
       </c>
-    </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K64" s="42" t="s">
+        <v>489</v>
+      </c>
+      <c r="L64" s="44" t="str">
+        <f t="shared" si="0"/>
+        <v>*P0370*</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="6"/>
       <c r="B65" s="6"/>
       <c r="C65" s="12" t="s">
@@ -3650,8 +5298,15 @@
       <c r="J65" s="15">
         <v>200</v>
       </c>
-    </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K65" s="42" t="s">
+        <v>490</v>
+      </c>
+      <c r="L65" s="44" t="str">
+        <f t="shared" si="0"/>
+        <v>*P0365*</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="6"/>
       <c r="B66" s="6"/>
       <c r="C66" s="7" t="s">
@@ -3672,8 +5327,15 @@
       <c r="J66" s="10">
         <v>180</v>
       </c>
-    </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K66" s="42" t="s">
+        <v>491</v>
+      </c>
+      <c r="L66" s="44" t="str">
+        <f t="shared" ref="L66:L129" si="1">"*"&amp;UPPER(K66)&amp;"*"</f>
+        <v>*P0369*</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="6"/>
       <c r="B67" s="6"/>
       <c r="C67" s="20" t="s">
@@ -3698,8 +5360,15 @@
       <c r="J67" s="15">
         <v>220</v>
       </c>
-    </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K67" s="42" t="s">
+        <v>492</v>
+      </c>
+      <c r="L67" s="44" t="str">
+        <f t="shared" si="1"/>
+        <v>*P0355*</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="6"/>
       <c r="B68" s="6"/>
       <c r="C68" s="20" t="s">
@@ -3724,8 +5393,15 @@
       <c r="J68" s="15">
         <v>200</v>
       </c>
-    </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K68" s="42" t="s">
+        <v>493</v>
+      </c>
+      <c r="L68" s="44" t="str">
+        <f t="shared" si="1"/>
+        <v>*P0357*</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="6"/>
       <c r="B69" s="6"/>
       <c r="C69" s="20" t="s">
@@ -3750,8 +5426,15 @@
       <c r="J69" s="15">
         <v>200</v>
       </c>
-    </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K69" s="42" t="s">
+        <v>494</v>
+      </c>
+      <c r="L69" s="44" t="str">
+        <f t="shared" si="1"/>
+        <v>*P0358*</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="6"/>
       <c r="B70" s="6"/>
       <c r="C70" s="19" t="s">
@@ -3776,8 +5459,15 @@
       <c r="J70" s="10">
         <v>220</v>
       </c>
-    </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K70" s="42" t="s">
+        <v>495</v>
+      </c>
+      <c r="L70" s="44" t="str">
+        <f t="shared" si="1"/>
+        <v>*P0361*</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="6"/>
       <c r="B71" s="6"/>
       <c r="C71" s="19" t="s">
@@ -3802,8 +5492,15 @@
       <c r="J71" s="10">
         <v>200</v>
       </c>
-    </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K71" s="42" t="s">
+        <v>496</v>
+      </c>
+      <c r="L71" s="44" t="str">
+        <f t="shared" si="1"/>
+        <v>*P0359*</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="6"/>
       <c r="B72" s="6"/>
       <c r="C72" s="19" t="s">
@@ -3828,8 +5525,15 @@
       <c r="J72" s="10">
         <v>260</v>
       </c>
-    </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K72" s="42" t="s">
+        <v>497</v>
+      </c>
+      <c r="L72" s="44" t="str">
+        <f t="shared" si="1"/>
+        <v>*P0360*</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="6"/>
       <c r="B73" s="6"/>
       <c r="C73" s="19" t="s">
@@ -3854,8 +5558,15 @@
       <c r="J73" s="10">
         <v>200</v>
       </c>
-    </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K73" s="42" t="s">
+        <v>498</v>
+      </c>
+      <c r="L73" s="44" t="str">
+        <f t="shared" si="1"/>
+        <v>*P0362*</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="6"/>
       <c r="B74" s="6"/>
       <c r="C74" s="20" t="s">
@@ -3880,8 +5591,15 @@
       <c r="J74" s="15">
         <v>260</v>
       </c>
-    </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K74" s="42" t="s">
+        <v>499</v>
+      </c>
+      <c r="L74" s="44" t="str">
+        <f t="shared" si="1"/>
+        <v>*P0289*</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="6"/>
       <c r="B75" s="6"/>
       <c r="C75" s="20" t="s">
@@ -3906,8 +5624,15 @@
       <c r="J75" s="15">
         <v>260</v>
       </c>
-    </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K75" s="42" t="s">
+        <v>500</v>
+      </c>
+      <c r="L75" s="44" t="str">
+        <f t="shared" si="1"/>
+        <v>*P0354*</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="6"/>
       <c r="B76" s="6"/>
       <c r="C76" s="19" t="s">
@@ -3932,8 +5657,15 @@
       <c r="J76" s="10">
         <v>300</v>
       </c>
-    </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K76" s="42" t="s">
+        <v>501</v>
+      </c>
+      <c r="L76" s="44" t="str">
+        <f t="shared" si="1"/>
+        <v>*P0291*</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="6"/>
       <c r="B77" s="6"/>
       <c r="C77" s="19" t="s">
@@ -3958,8 +5690,15 @@
       <c r="J77" s="10">
         <v>140</v>
       </c>
-    </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K77" s="42" t="s">
+        <v>502</v>
+      </c>
+      <c r="L77" s="44" t="str">
+        <f t="shared" si="1"/>
+        <v>*P0077*</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="6"/>
       <c r="B78" s="6"/>
       <c r="C78" s="19" t="s">
@@ -3984,8 +5723,15 @@
       <c r="J78" s="10">
         <v>230</v>
       </c>
-    </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K78" s="42" t="s">
+        <v>503</v>
+      </c>
+      <c r="L78" s="44" t="str">
+        <f t="shared" si="1"/>
+        <v>*P0294*</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="6"/>
       <c r="B79" s="6"/>
       <c r="C79" s="19" t="s">
@@ -4010,8 +5756,15 @@
       <c r="J79" s="10">
         <v>100</v>
       </c>
-    </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K79" s="42" t="s">
+        <v>504</v>
+      </c>
+      <c r="L79" s="44" t="str">
+        <f t="shared" si="1"/>
+        <v>*P0293*</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="6"/>
       <c r="B80" s="6"/>
       <c r="C80" s="19" t="s">
@@ -4036,8 +5789,15 @@
       <c r="J80" s="10">
         <v>100</v>
       </c>
-    </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K80" s="42" t="s">
+        <v>505</v>
+      </c>
+      <c r="L80" s="44" t="str">
+        <f t="shared" si="1"/>
+        <v>*P0292*</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="6"/>
       <c r="B81" s="6"/>
       <c r="C81" s="20" t="s">
@@ -4062,8 +5822,15 @@
       <c r="J81" s="15">
         <v>70</v>
       </c>
-    </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K81" s="42" t="s">
+        <v>506</v>
+      </c>
+      <c r="L81" s="44" t="str">
+        <f t="shared" si="1"/>
+        <v>*P0045*</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="6"/>
       <c r="B82" s="6"/>
       <c r="C82" s="20" t="s">
@@ -4088,8 +5855,15 @@
       <c r="J82" s="15">
         <v>70</v>
       </c>
-    </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K82" s="42" t="s">
+        <v>507</v>
+      </c>
+      <c r="L82" s="44" t="str">
+        <f t="shared" si="1"/>
+        <v>*P0290*</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="6"/>
       <c r="B83" s="6"/>
       <c r="C83" s="19" t="s">
@@ -4114,8 +5888,15 @@
       <c r="J83" s="10">
         <v>200</v>
       </c>
-    </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K83" s="42" t="s">
+        <v>508</v>
+      </c>
+      <c r="L83" s="44" t="str">
+        <f t="shared" si="1"/>
+        <v>*P0106*</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="6"/>
       <c r="B84" s="6"/>
       <c r="C84" s="20" t="s">
@@ -4140,8 +5921,15 @@
       <c r="J84" s="15">
         <v>320</v>
       </c>
-    </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K84" s="42" t="s">
+        <v>509</v>
+      </c>
+      <c r="L84" s="44" t="str">
+        <f t="shared" si="1"/>
+        <v>*P0356*</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="6"/>
       <c r="B85" s="6"/>
       <c r="C85" s="21" t="s">
@@ -4166,8 +5954,15 @@
       <c r="J85" s="9">
         <v>270</v>
       </c>
-    </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K85" s="42" t="s">
+        <v>510</v>
+      </c>
+      <c r="L85" s="44" t="str">
+        <f t="shared" si="1"/>
+        <v>*P0311*</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="6"/>
       <c r="B86" s="6"/>
       <c r="C86" s="21" t="s">
@@ -4192,8 +5987,15 @@
       <c r="J86" s="9">
         <v>270</v>
       </c>
-    </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K86" s="42" t="s">
+        <v>511</v>
+      </c>
+      <c r="L86" s="44" t="str">
+        <f t="shared" si="1"/>
+        <v>*P0312*</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="6"/>
       <c r="B87" s="6"/>
       <c r="C87" s="21" t="s">
@@ -4218,8 +6020,15 @@
       <c r="J87" s="9">
         <v>270</v>
       </c>
-    </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K87" s="42" t="s">
+        <v>512</v>
+      </c>
+      <c r="L87" s="44" t="str">
+        <f t="shared" si="1"/>
+        <v>*P0313*</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="6"/>
       <c r="B88" s="6"/>
       <c r="C88" s="21" t="s">
@@ -4244,8 +6053,15 @@
       <c r="J88" s="9">
         <v>270</v>
       </c>
-    </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K88" s="42" t="s">
+        <v>513</v>
+      </c>
+      <c r="L88" s="44" t="str">
+        <f t="shared" si="1"/>
+        <v>*P0310*</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="6"/>
       <c r="B89" s="6"/>
       <c r="C89" s="21" t="s">
@@ -4270,8 +6086,15 @@
       <c r="J89" s="9">
         <v>270</v>
       </c>
-    </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K89" s="42" t="s">
+        <v>514</v>
+      </c>
+      <c r="L89" s="44" t="str">
+        <f t="shared" si="1"/>
+        <v>*P0314*</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="6"/>
       <c r="B90" s="6"/>
       <c r="C90" s="23" t="s">
@@ -4296,8 +6119,15 @@
       <c r="J90" s="10">
         <v>200</v>
       </c>
-    </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K90" s="42" t="s">
+        <v>515</v>
+      </c>
+      <c r="L90" s="44" t="str">
+        <f t="shared" si="1"/>
+        <v>*P0287*</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="6"/>
       <c r="B91" s="6"/>
       <c r="C91" s="23" t="s">
@@ -4323,8 +6153,15 @@
       <c r="J91" s="10">
         <v>280</v>
       </c>
-    </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K91" s="42" t="s">
+        <v>516</v>
+      </c>
+      <c r="L91" s="44" t="str">
+        <f t="shared" si="1"/>
+        <v>*P0279*</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="6"/>
       <c r="B92" s="6"/>
       <c r="C92" s="23" t="s">
@@ -4349,8 +6186,15 @@
       <c r="J92" s="10">
         <v>120</v>
       </c>
-    </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K92" s="42" t="s">
+        <v>517</v>
+      </c>
+      <c r="L92" s="44" t="str">
+        <f t="shared" si="1"/>
+        <v>*P0280*</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="6"/>
       <c r="B93" s="6"/>
       <c r="C93" s="23" t="s">
@@ -4375,8 +6219,15 @@
       <c r="J93" s="10">
         <v>120</v>
       </c>
-    </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K93" s="42" t="s">
+        <v>518</v>
+      </c>
+      <c r="L93" s="44" t="str">
+        <f t="shared" si="1"/>
+        <v>*P0282*</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="6"/>
       <c r="B94" s="6"/>
       <c r="C94" s="23" t="s">
@@ -4401,8 +6252,15 @@
       <c r="J94" s="10">
         <v>120</v>
       </c>
-    </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K94" s="42" t="s">
+        <v>519</v>
+      </c>
+      <c r="L94" s="44" t="str">
+        <f t="shared" si="1"/>
+        <v>*P0281*</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="6"/>
       <c r="B95" s="6"/>
       <c r="C95" s="23" t="s">
@@ -4427,8 +6285,15 @@
       <c r="J95" s="10">
         <v>200</v>
       </c>
-    </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K95" s="42" t="s">
+        <v>520</v>
+      </c>
+      <c r="L95" s="44" t="str">
+        <f t="shared" si="1"/>
+        <v>*P0285*</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="6"/>
       <c r="B96" s="6"/>
       <c r="C96" s="23" t="s">
@@ -4453,8 +6318,15 @@
       <c r="J96" s="10">
         <v>200</v>
       </c>
-    </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K96" s="42" t="s">
+        <v>521</v>
+      </c>
+      <c r="L96" s="44" t="str">
+        <f t="shared" si="1"/>
+        <v>*P0288*</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="6"/>
       <c r="B97" s="6"/>
       <c r="C97" s="23" t="s">
@@ -4479,8 +6351,15 @@
       <c r="J97" s="10">
         <v>200</v>
       </c>
-    </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K97" s="42" t="s">
+        <v>522</v>
+      </c>
+      <c r="L97" s="44" t="str">
+        <f t="shared" si="1"/>
+        <v>*P0286*</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="6"/>
       <c r="B98" s="6"/>
       <c r="C98" s="23" t="s">
@@ -4505,8 +6384,15 @@
       <c r="J98" s="10">
         <v>200</v>
       </c>
-    </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K98" s="42" t="s">
+        <v>523</v>
+      </c>
+      <c r="L98" s="44" t="str">
+        <f t="shared" si="1"/>
+        <v>*P0284*</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="6"/>
       <c r="B99" s="6"/>
       <c r="C99" s="23" t="s">
@@ -4531,8 +6417,15 @@
       <c r="J99" s="10">
         <v>200</v>
       </c>
-    </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K99" s="42" t="s">
+        <v>524</v>
+      </c>
+      <c r="L99" s="44" t="str">
+        <f t="shared" si="1"/>
+        <v>*P0283*</v>
+      </c>
+    </row>
+    <row r="100" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="6"/>
       <c r="B100" s="6"/>
       <c r="C100" s="23" t="s">
@@ -4557,8 +6450,15 @@
       <c r="J100" s="10">
         <v>130</v>
       </c>
-    </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K100" s="42" t="s">
+        <v>525</v>
+      </c>
+      <c r="L100" s="44" t="str">
+        <f t="shared" si="1"/>
+        <v>*P0076*</v>
+      </c>
+    </row>
+    <row r="101" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="6"/>
       <c r="B101" s="6"/>
       <c r="C101" s="23" t="s">
@@ -4583,8 +6483,15 @@
       <c r="J101" s="10">
         <v>180</v>
       </c>
-    </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K101" s="42" t="s">
+        <v>526</v>
+      </c>
+      <c r="L101" s="44" t="str">
+        <f t="shared" si="1"/>
+        <v>*P0103*</v>
+      </c>
+    </row>
+    <row r="102" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="6"/>
       <c r="B102" s="6"/>
       <c r="C102" s="23" t="s">
@@ -4609,8 +6516,15 @@
       <c r="J102" s="10">
         <v>250</v>
       </c>
-    </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K102" s="42" t="s">
+        <v>527</v>
+      </c>
+      <c r="L102" s="44" t="str">
+        <f t="shared" si="1"/>
+        <v>*P0353*</v>
+      </c>
+    </row>
+    <row r="103" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="6"/>
       <c r="B103" s="6"/>
       <c r="C103" s="23" t="s">
@@ -4635,8 +6549,15 @@
       <c r="J103" s="10">
         <v>250</v>
       </c>
-    </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K103" s="42" t="s">
+        <v>528</v>
+      </c>
+      <c r="L103" s="44" t="str">
+        <f t="shared" si="1"/>
+        <v>*P0352*</v>
+      </c>
+    </row>
+    <row r="104" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="6"/>
       <c r="B104" s="6"/>
       <c r="C104" s="23" t="s">
@@ -4661,8 +6582,15 @@
       <c r="J104" s="10">
         <v>250</v>
       </c>
-    </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K104" s="42" t="s">
+        <v>529</v>
+      </c>
+      <c r="L104" s="44" t="str">
+        <f t="shared" si="1"/>
+        <v>*P0008*</v>
+      </c>
+    </row>
+    <row r="105" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="6"/>
       <c r="B105" s="6"/>
       <c r="C105" s="23" t="s">
@@ -4687,8 +6615,15 @@
       <c r="J105" s="10">
         <v>180</v>
       </c>
-    </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K105" s="42" t="s">
+        <v>530</v>
+      </c>
+      <c r="L105" s="44" t="str">
+        <f t="shared" si="1"/>
+        <v>*P0277*</v>
+      </c>
+    </row>
+    <row r="106" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="6"/>
       <c r="B106" s="6"/>
       <c r="C106" s="23" t="s">
@@ -4713,8 +6648,15 @@
       <c r="J106" s="10">
         <v>180</v>
       </c>
-    </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K106" s="42" t="s">
+        <v>531</v>
+      </c>
+      <c r="L106" s="44" t="str">
+        <f t="shared" si="1"/>
+        <v>*P0278*</v>
+      </c>
+    </row>
+    <row r="107" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="6"/>
       <c r="B107" s="6"/>
       <c r="C107" s="23" t="s">
@@ -4739,8 +6681,15 @@
       <c r="J107" s="10">
         <v>180</v>
       </c>
-    </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K107" s="42" t="s">
+        <v>532</v>
+      </c>
+      <c r="L107" s="44" t="str">
+        <f t="shared" si="1"/>
+        <v>*P0042*</v>
+      </c>
+    </row>
+    <row r="108" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="6"/>
       <c r="B108" s="6"/>
       <c r="C108" s="23" t="s">
@@ -4765,8 +6714,15 @@
       <c r="J108" s="10">
         <v>200</v>
       </c>
-    </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K108" s="42" t="s">
+        <v>533</v>
+      </c>
+      <c r="L108" s="44" t="str">
+        <f t="shared" si="1"/>
+        <v>*P0132*</v>
+      </c>
+    </row>
+    <row r="109" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="6"/>
       <c r="B109" s="6"/>
       <c r="C109" s="23" t="s">
@@ -4791,8 +6747,15 @@
       <c r="J109" s="10">
         <v>200</v>
       </c>
-    </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K109" s="42" t="s">
+        <v>534</v>
+      </c>
+      <c r="L109" s="44" t="str">
+        <f t="shared" si="1"/>
+        <v>*P0131*</v>
+      </c>
+    </row>
+    <row r="110" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="6"/>
       <c r="B110" s="6"/>
       <c r="C110" s="23" t="s">
@@ -4817,8 +6780,15 @@
       <c r="J110" s="10">
         <v>200</v>
       </c>
-    </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K110" s="42" t="s">
+        <v>535</v>
+      </c>
+      <c r="L110" s="44" t="str">
+        <f t="shared" si="1"/>
+        <v>*P0115*</v>
+      </c>
+    </row>
+    <row r="111" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="6"/>
       <c r="B111" s="6"/>
       <c r="C111" s="23" t="s">
@@ -4843,8 +6813,15 @@
       <c r="J111" s="10">
         <v>200</v>
       </c>
-    </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K111" s="42" t="s">
+        <v>536</v>
+      </c>
+      <c r="L111" s="44" t="str">
+        <f t="shared" si="1"/>
+        <v>*P0137*</v>
+      </c>
+    </row>
+    <row r="112" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="6"/>
       <c r="B112" s="6"/>
       <c r="C112" s="23" t="s">
@@ -4869,8 +6846,15 @@
       <c r="J112" s="10">
         <v>200</v>
       </c>
-    </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K112" s="42" t="s">
+        <v>537</v>
+      </c>
+      <c r="L112" s="44" t="str">
+        <f t="shared" si="1"/>
+        <v>*P0134*</v>
+      </c>
+    </row>
+    <row r="113" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="6"/>
       <c r="B113" s="6"/>
       <c r="C113" s="23" t="s">
@@ -4895,8 +6879,15 @@
       <c r="J113" s="10">
         <v>200</v>
       </c>
-    </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K113" s="42" t="s">
+        <v>538</v>
+      </c>
+      <c r="L113" s="44" t="str">
+        <f t="shared" si="1"/>
+        <v>*P0120*</v>
+      </c>
+    </row>
+    <row r="114" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="6"/>
       <c r="B114" s="6"/>
       <c r="C114" s="23" t="s">
@@ -4921,8 +6912,15 @@
       <c r="J114" s="10">
         <v>200</v>
       </c>
-    </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K114" s="42" t="s">
+        <v>539</v>
+      </c>
+      <c r="L114" s="44" t="str">
+        <f t="shared" si="1"/>
+        <v>*P0127*</v>
+      </c>
+    </row>
+    <row r="115" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="6"/>
       <c r="B115" s="6"/>
       <c r="C115" s="23" t="s">
@@ -4947,8 +6945,15 @@
       <c r="J115" s="10">
         <v>200</v>
       </c>
-    </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K115" s="42" t="s">
+        <v>540</v>
+      </c>
+      <c r="L115" s="44" t="str">
+        <f t="shared" si="1"/>
+        <v>*P0124*</v>
+      </c>
+    </row>
+    <row r="116" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="6"/>
       <c r="B116" s="6"/>
       <c r="C116" s="23" t="s">
@@ -4973,8 +6978,15 @@
       <c r="J116" s="10">
         <v>200</v>
       </c>
-    </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K116" s="42" t="s">
+        <v>541</v>
+      </c>
+      <c r="L116" s="44" t="str">
+        <f t="shared" si="1"/>
+        <v>*P0121*</v>
+      </c>
+    </row>
+    <row r="117" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="6"/>
       <c r="B117" s="6"/>
       <c r="C117" s="23" t="s">
@@ -4999,8 +7011,15 @@
       <c r="J117" s="10">
         <v>200</v>
       </c>
-    </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K117" s="42" t="s">
+        <v>542</v>
+      </c>
+      <c r="L117" s="44" t="str">
+        <f t="shared" si="1"/>
+        <v>*P0112*</v>
+      </c>
+    </row>
+    <row r="118" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="6"/>
       <c r="B118" s="6"/>
       <c r="C118" s="23" t="s">
@@ -5025,8 +7044,15 @@
       <c r="J118" s="10">
         <v>200</v>
       </c>
-    </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K118" s="42" t="s">
+        <v>543</v>
+      </c>
+      <c r="L118" s="44" t="str">
+        <f t="shared" si="1"/>
+        <v>*P0109*</v>
+      </c>
+    </row>
+    <row r="119" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="6"/>
       <c r="B119" s="6"/>
       <c r="C119" s="23" t="s">
@@ -5051,8 +7077,15 @@
       <c r="J119" s="10">
         <v>200</v>
       </c>
-    </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K119" s="42" t="s">
+        <v>544</v>
+      </c>
+      <c r="L119" s="44" t="str">
+        <f t="shared" si="1"/>
+        <v>*P0111*</v>
+      </c>
+    </row>
+    <row r="120" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="6"/>
       <c r="B120" s="6"/>
       <c r="C120" s="23" t="s">
@@ -5077,8 +7110,15 @@
       <c r="J120" s="10">
         <v>200</v>
       </c>
-    </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K120" s="42" t="s">
+        <v>545</v>
+      </c>
+      <c r="L120" s="44" t="str">
+        <f t="shared" si="1"/>
+        <v>*P0116*</v>
+      </c>
+    </row>
+    <row r="121" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="6"/>
       <c r="B121" s="6"/>
       <c r="C121" s="23" t="s">
@@ -5103,8 +7143,15 @@
       <c r="J121" s="10">
         <v>200</v>
       </c>
-    </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K121" s="42" t="s">
+        <v>546</v>
+      </c>
+      <c r="L121" s="44" t="str">
+        <f t="shared" si="1"/>
+        <v>*P0118*</v>
+      </c>
+    </row>
+    <row r="122" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="6"/>
       <c r="B122" s="6"/>
       <c r="C122" s="23" t="s">
@@ -5129,8 +7176,15 @@
       <c r="J122" s="10">
         <v>200</v>
       </c>
-    </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K122" s="42" t="s">
+        <v>547</v>
+      </c>
+      <c r="L122" s="44" t="str">
+        <f t="shared" si="1"/>
+        <v>*P0130*</v>
+      </c>
+    </row>
+    <row r="123" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="6"/>
       <c r="B123" s="6"/>
       <c r="C123" s="23" t="s">
@@ -5155,8 +7209,15 @@
       <c r="J123" s="10">
         <v>200</v>
       </c>
-    </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K123" s="42" t="s">
+        <v>548</v>
+      </c>
+      <c r="L123" s="44" t="str">
+        <f t="shared" si="1"/>
+        <v>*P0126*</v>
+      </c>
+    </row>
+    <row r="124" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="6"/>
       <c r="B124" s="6"/>
       <c r="C124" s="23" t="s">
@@ -5181,8 +7242,15 @@
       <c r="J124" s="10">
         <v>350</v>
       </c>
-    </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K124" s="42" t="s">
+        <v>549</v>
+      </c>
+      <c r="L124" s="44" t="str">
+        <f t="shared" si="1"/>
+        <v>*P0125*</v>
+      </c>
+    </row>
+    <row r="125" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="6"/>
       <c r="B125" s="6"/>
       <c r="C125" s="23" t="s">
@@ -5207,8 +7275,15 @@
       <c r="J125" s="10">
         <v>350</v>
       </c>
-    </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K125" s="42" t="s">
+        <v>550</v>
+      </c>
+      <c r="L125" s="44" t="str">
+        <f t="shared" si="1"/>
+        <v>*P0135*</v>
+      </c>
+    </row>
+    <row r="126" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="6"/>
       <c r="B126" s="6"/>
       <c r="C126" s="23" t="s">
@@ -5233,8 +7308,15 @@
       <c r="J126" s="10">
         <v>350</v>
       </c>
-    </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K126" s="42" t="s">
+        <v>551</v>
+      </c>
+      <c r="L126" s="44" t="str">
+        <f t="shared" si="1"/>
+        <v>*P0136*</v>
+      </c>
+    </row>
+    <row r="127" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="6"/>
       <c r="B127" s="6"/>
       <c r="C127" s="23" t="s">
@@ -5259,8 +7341,15 @@
       <c r="J127" s="10">
         <v>350</v>
       </c>
-    </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K127" s="42" t="s">
+        <v>552</v>
+      </c>
+      <c r="L127" s="44" t="str">
+        <f t="shared" si="1"/>
+        <v>*P0129*</v>
+      </c>
+    </row>
+    <row r="128" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="6"/>
       <c r="B128" s="6"/>
       <c r="C128" s="23" t="s">
@@ -5285,8 +7374,15 @@
       <c r="J128" s="10">
         <v>350</v>
       </c>
-    </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K128" s="42" t="s">
+        <v>553</v>
+      </c>
+      <c r="L128" s="44" t="str">
+        <f t="shared" si="1"/>
+        <v>*P0113*</v>
+      </c>
+    </row>
+    <row r="129" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="6"/>
       <c r="B129" s="6"/>
       <c r="C129" s="23" t="s">
@@ -5311,8 +7407,15 @@
       <c r="J129" s="10">
         <v>350</v>
       </c>
-    </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K129" s="42" t="s">
+        <v>554</v>
+      </c>
+      <c r="L129" s="44" t="str">
+        <f t="shared" si="1"/>
+        <v>*P0114*</v>
+      </c>
+    </row>
+    <row r="130" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="6"/>
       <c r="B130" s="6"/>
       <c r="C130" s="23" t="s">
@@ -5337,8 +7440,15 @@
       <c r="J130" s="10">
         <v>350</v>
       </c>
-    </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K130" s="42" t="s">
+        <v>555</v>
+      </c>
+      <c r="L130" s="44" t="str">
+        <f t="shared" ref="L130:L193" si="2">"*"&amp;UPPER(K130)&amp;"*"</f>
+        <v>*P0119*</v>
+      </c>
+    </row>
+    <row r="131" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="6"/>
       <c r="B131" s="6"/>
       <c r="C131" s="23" t="s">
@@ -5363,8 +7473,15 @@
       <c r="J131" s="10">
         <v>350</v>
       </c>
-    </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K131" s="42" t="s">
+        <v>556</v>
+      </c>
+      <c r="L131" s="44" t="str">
+        <f t="shared" si="2"/>
+        <v>*P0133*</v>
+      </c>
+    </row>
+    <row r="132" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="6"/>
       <c r="B132" s="6"/>
       <c r="C132" s="23" t="s">
@@ -5389,8 +7506,15 @@
       <c r="J132" s="10">
         <v>350</v>
       </c>
-    </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K132" s="42" t="s">
+        <v>557</v>
+      </c>
+      <c r="L132" s="44" t="str">
+        <f t="shared" si="2"/>
+        <v>*P0117*</v>
+      </c>
+    </row>
+    <row r="133" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="6"/>
       <c r="B133" s="6"/>
       <c r="C133" s="23" t="s">
@@ -5415,8 +7539,15 @@
       <c r="J133" s="10">
         <v>350</v>
       </c>
-    </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K133" s="42" t="s">
+        <v>558</v>
+      </c>
+      <c r="L133" s="44" t="str">
+        <f t="shared" si="2"/>
+        <v>*P0128*</v>
+      </c>
+    </row>
+    <row r="134" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="6"/>
       <c r="B134" s="6"/>
       <c r="C134" s="23" t="s">
@@ -5441,8 +7572,15 @@
       <c r="J134" s="10">
         <v>350</v>
       </c>
-    </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K134" s="42" t="s">
+        <v>559</v>
+      </c>
+      <c r="L134" s="44" t="str">
+        <f t="shared" si="2"/>
+        <v>*P0123*</v>
+      </c>
+    </row>
+    <row r="135" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="6"/>
       <c r="B135" s="6"/>
       <c r="C135" s="23" t="s">
@@ -5467,8 +7605,15 @@
       <c r="J135" s="10">
         <v>350</v>
       </c>
-    </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K135" s="42" t="s">
+        <v>560</v>
+      </c>
+      <c r="L135" s="44" t="str">
+        <f t="shared" si="2"/>
+        <v>*P0122*</v>
+      </c>
+    </row>
+    <row r="136" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="6"/>
       <c r="B136" s="6"/>
       <c r="C136" s="23" t="s">
@@ -5493,8 +7638,15 @@
       <c r="J136" s="10">
         <v>350</v>
       </c>
-    </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K136" s="42" t="s">
+        <v>561</v>
+      </c>
+      <c r="L136" s="44" t="str">
+        <f t="shared" si="2"/>
+        <v>*P0110*</v>
+      </c>
+    </row>
+    <row r="137" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="6"/>
       <c r="B137" s="6"/>
       <c r="C137" s="24" t="s">
@@ -5519,8 +7671,15 @@
       <c r="J137" s="10">
         <v>350</v>
       </c>
-    </row>
-    <row r="138" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K137" s="42" t="s">
+        <v>562</v>
+      </c>
+      <c r="L137" s="44" t="str">
+        <f t="shared" si="2"/>
+        <v>*P0017*</v>
+      </c>
+    </row>
+    <row r="138" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="6"/>
       <c r="B138" s="6"/>
       <c r="C138" s="24" t="s">
@@ -5545,8 +7704,15 @@
       <c r="J138" s="10">
         <v>350</v>
       </c>
-    </row>
-    <row r="139" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K138" s="42" t="s">
+        <v>563</v>
+      </c>
+      <c r="L138" s="44" t="str">
+        <f t="shared" si="2"/>
+        <v>*P0018*</v>
+      </c>
+    </row>
+    <row r="139" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="6"/>
       <c r="B139" s="6"/>
       <c r="C139" s="24" t="s">
@@ -5571,8 +7737,15 @@
       <c r="J139" s="10">
         <v>200</v>
       </c>
-    </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K139" s="42" t="s">
+        <v>564</v>
+      </c>
+      <c r="L139" s="44" t="str">
+        <f t="shared" si="2"/>
+        <v>*P0019*</v>
+      </c>
+    </row>
+    <row r="140" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="6"/>
       <c r="B140" s="6"/>
       <c r="C140" s="24" t="s">
@@ -5597,8 +7770,15 @@
       <c r="J140" s="10">
         <v>350</v>
       </c>
-    </row>
-    <row r="141" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K140" s="42" t="s">
+        <v>565</v>
+      </c>
+      <c r="L140" s="44" t="str">
+        <f t="shared" si="2"/>
+        <v>*P0020*</v>
+      </c>
+    </row>
+    <row r="141" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="6"/>
       <c r="B141" s="6"/>
       <c r="C141" s="24" t="s">
@@ -5623,8 +7803,15 @@
       <c r="J141" s="10">
         <v>350</v>
       </c>
-    </row>
-    <row r="142" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K141" s="42" t="s">
+        <v>566</v>
+      </c>
+      <c r="L141" s="44" t="str">
+        <f t="shared" si="2"/>
+        <v>*P0021*</v>
+      </c>
+    </row>
+    <row r="142" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="6"/>
       <c r="B142" s="6"/>
       <c r="C142" s="24" t="s">
@@ -5649,8 +7836,15 @@
       <c r="J142" s="10">
         <v>200</v>
       </c>
-    </row>
-    <row r="143" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K142" s="42" t="s">
+        <v>567</v>
+      </c>
+      <c r="L142" s="44" t="str">
+        <f t="shared" si="2"/>
+        <v>*P0022*</v>
+      </c>
+    </row>
+    <row r="143" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="6"/>
       <c r="B143" s="6"/>
       <c r="C143" s="24" t="s">
@@ -5675,8 +7869,15 @@
       <c r="J143" s="10">
         <v>350</v>
       </c>
-    </row>
-    <row r="144" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K143" s="42" t="s">
+        <v>568</v>
+      </c>
+      <c r="L143" s="44" t="str">
+        <f t="shared" si="2"/>
+        <v>*P0023*</v>
+      </c>
+    </row>
+    <row r="144" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="6"/>
       <c r="B144" s="6"/>
       <c r="C144" s="24" t="s">
@@ -5701,8 +7902,15 @@
       <c r="J144" s="10">
         <v>200</v>
       </c>
-    </row>
-    <row r="145" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K144" s="42" t="s">
+        <v>569</v>
+      </c>
+      <c r="L144" s="44" t="str">
+        <f t="shared" si="2"/>
+        <v>*P0024*</v>
+      </c>
+    </row>
+    <row r="145" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="6"/>
       <c r="B145" s="6"/>
       <c r="C145" s="24" t="s">
@@ -5727,8 +7935,15 @@
       <c r="J145" s="10">
         <v>350</v>
       </c>
-    </row>
-    <row r="146" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K145" s="42" t="s">
+        <v>570</v>
+      </c>
+      <c r="L145" s="44" t="str">
+        <f t="shared" si="2"/>
+        <v>*P0025*</v>
+      </c>
+    </row>
+    <row r="146" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="6"/>
       <c r="B146" s="6"/>
       <c r="C146" s="24" t="s">
@@ -5753,8 +7968,15 @@
       <c r="J146" s="10">
         <v>200</v>
       </c>
-    </row>
-    <row r="147" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K146" s="42" t="s">
+        <v>571</v>
+      </c>
+      <c r="L146" s="44" t="str">
+        <f t="shared" si="2"/>
+        <v>*P0026*</v>
+      </c>
+    </row>
+    <row r="147" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="6"/>
       <c r="B147" s="6"/>
       <c r="C147" s="24" t="s">
@@ -5779,8 +8001,15 @@
       <c r="J147" s="10">
         <v>350</v>
       </c>
-    </row>
-    <row r="148" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K147" s="42" t="s">
+        <v>572</v>
+      </c>
+      <c r="L147" s="44" t="str">
+        <f t="shared" si="2"/>
+        <v>*P0027*</v>
+      </c>
+    </row>
+    <row r="148" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="6"/>
       <c r="B148" s="6"/>
       <c r="C148" s="24" t="s">
@@ -5805,8 +8034,15 @@
       <c r="J148" s="10">
         <v>350</v>
       </c>
-    </row>
-    <row r="149" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K148" s="42" t="s">
+        <v>573</v>
+      </c>
+      <c r="L148" s="44" t="str">
+        <f t="shared" si="2"/>
+        <v>*P0028*</v>
+      </c>
+    </row>
+    <row r="149" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="6"/>
       <c r="B149" s="6"/>
       <c r="C149" s="24" t="s">
@@ -5827,8 +8063,15 @@
       <c r="J149" s="10">
         <v>200</v>
       </c>
-    </row>
-    <row r="150" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K149" s="42" t="s">
+        <v>574</v>
+      </c>
+      <c r="L149" s="44" t="str">
+        <f t="shared" si="2"/>
+        <v>*P0029*</v>
+      </c>
+    </row>
+    <row r="150" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="6"/>
       <c r="B150" s="6"/>
       <c r="C150" s="24" t="s">
@@ -5853,8 +8096,15 @@
       <c r="J150" s="10">
         <v>350</v>
       </c>
-    </row>
-    <row r="151" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K150" s="42" t="s">
+        <v>575</v>
+      </c>
+      <c r="L150" s="44" t="str">
+        <f t="shared" si="2"/>
+        <v>*P0030*</v>
+      </c>
+    </row>
+    <row r="151" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="6"/>
       <c r="B151" s="6"/>
       <c r="C151" s="24" t="s">
@@ -5879,8 +8129,15 @@
       <c r="J151" s="10">
         <v>350</v>
       </c>
-    </row>
-    <row r="152" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K151" s="42" t="s">
+        <v>576</v>
+      </c>
+      <c r="L151" s="44" t="str">
+        <f t="shared" si="2"/>
+        <v>*P0031*</v>
+      </c>
+    </row>
+    <row r="152" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="6"/>
       <c r="B152" s="6"/>
       <c r="C152" s="24" t="s">
@@ -5905,8 +8162,15 @@
       <c r="J152" s="10">
         <v>350</v>
       </c>
-    </row>
-    <row r="153" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K152" s="42" t="s">
+        <v>577</v>
+      </c>
+      <c r="L152" s="44" t="str">
+        <f t="shared" si="2"/>
+        <v>*P0032*</v>
+      </c>
+    </row>
+    <row r="153" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="6"/>
       <c r="B153" s="6"/>
       <c r="C153" s="24" t="s">
@@ -5931,8 +8195,15 @@
       <c r="J153" s="10">
         <v>350</v>
       </c>
-    </row>
-    <row r="154" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K153" s="42" t="s">
+        <v>578</v>
+      </c>
+      <c r="L153" s="44" t="str">
+        <f t="shared" si="2"/>
+        <v>*P0033*</v>
+      </c>
+    </row>
+    <row r="154" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="6"/>
       <c r="B154" s="6"/>
       <c r="C154" s="24" t="s">
@@ -5957,8 +8228,15 @@
       <c r="J154" s="10">
         <v>350</v>
       </c>
-    </row>
-    <row r="155" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K154" s="42" t="s">
+        <v>579</v>
+      </c>
+      <c r="L154" s="44" t="str">
+        <f t="shared" si="2"/>
+        <v>*P0034*</v>
+      </c>
+    </row>
+    <row r="155" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="6"/>
       <c r="B155" s="6"/>
       <c r="C155" s="24" t="s">
@@ -5983,8 +8261,15 @@
       <c r="J155" s="10">
         <v>200</v>
       </c>
-    </row>
-    <row r="156" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K155" s="42" t="s">
+        <v>580</v>
+      </c>
+      <c r="L155" s="44" t="str">
+        <f t="shared" si="2"/>
+        <v>*P0035*</v>
+      </c>
+    </row>
+    <row r="156" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="6"/>
       <c r="B156" s="6"/>
       <c r="C156" s="24" t="s">
@@ -6009,8 +8294,15 @@
       <c r="J156" s="10">
         <v>350</v>
       </c>
-    </row>
-    <row r="157" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K156" s="42" t="s">
+        <v>581</v>
+      </c>
+      <c r="L156" s="44" t="str">
+        <f t="shared" si="2"/>
+        <v>*P0036*</v>
+      </c>
+    </row>
+    <row r="157" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="6"/>
       <c r="B157" s="6"/>
       <c r="C157" s="24" t="s">
@@ -6035,8 +8327,15 @@
       <c r="J157" s="10">
         <v>350</v>
       </c>
-    </row>
-    <row r="158" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K157" s="42" t="s">
+        <v>582</v>
+      </c>
+      <c r="L157" s="44" t="str">
+        <f t="shared" si="2"/>
+        <v>*P0037*</v>
+      </c>
+    </row>
+    <row r="158" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="6"/>
       <c r="B158" s="6"/>
       <c r="C158" s="24" t="s">
@@ -6057,8 +8356,15 @@
       <c r="J158" s="10">
         <v>200</v>
       </c>
-    </row>
-    <row r="159" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K158" s="42" t="s">
+        <v>583</v>
+      </c>
+      <c r="L158" s="44" t="str">
+        <f t="shared" si="2"/>
+        <v>*P0038*</v>
+      </c>
+    </row>
+    <row r="159" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="6"/>
       <c r="B159" s="6"/>
       <c r="C159" s="24" t="s">
@@ -6083,8 +8389,15 @@
       <c r="J159" s="10">
         <v>350</v>
       </c>
-    </row>
-    <row r="160" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K159" s="42" t="s">
+        <v>584</v>
+      </c>
+      <c r="L159" s="44" t="str">
+        <f t="shared" si="2"/>
+        <v>*P0039*</v>
+      </c>
+    </row>
+    <row r="160" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="6"/>
       <c r="B160" s="6"/>
       <c r="C160" s="24" t="s">
@@ -6105,8 +8418,15 @@
       <c r="J160" s="10">
         <v>200</v>
       </c>
-    </row>
-    <row r="161" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K160" s="42" t="s">
+        <v>585</v>
+      </c>
+      <c r="L160" s="44" t="str">
+        <f t="shared" si="2"/>
+        <v>*P0040*</v>
+      </c>
+    </row>
+    <row r="161" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="6"/>
       <c r="B161" s="6"/>
       <c r="C161" s="24" t="s">
@@ -6131,8 +8451,15 @@
       <c r="J161" s="10">
         <v>350</v>
       </c>
-    </row>
-    <row r="162" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K161" s="42" t="s">
+        <v>586</v>
+      </c>
+      <c r="L161" s="44" t="str">
+        <f t="shared" si="2"/>
+        <v>*P0041*</v>
+      </c>
+    </row>
+    <row r="162" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="6"/>
       <c r="B162" s="6"/>
       <c r="C162" s="26" t="s">
@@ -6157,8 +8484,15 @@
       <c r="J162" s="10">
         <v>350</v>
       </c>
-    </row>
-    <row r="163" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K162" s="42" t="s">
+        <v>587</v>
+      </c>
+      <c r="L162" s="44" t="str">
+        <f t="shared" si="2"/>
+        <v>*P0377*</v>
+      </c>
+    </row>
+    <row r="163" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="6"/>
       <c r="B163" s="6"/>
       <c r="C163" s="26" t="s">
@@ -6183,8 +8517,15 @@
       <c r="J163" s="10">
         <v>250</v>
       </c>
-    </row>
-    <row r="164" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K163" s="42" t="s">
+        <v>588</v>
+      </c>
+      <c r="L163" s="44" t="str">
+        <f t="shared" si="2"/>
+        <v>*P0378*</v>
+      </c>
+    </row>
+    <row r="164" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="6"/>
       <c r="B164" s="6"/>
       <c r="C164" s="26" t="s">
@@ -6209,8 +8550,15 @@
       <c r="J164" s="10">
         <v>390</v>
       </c>
-    </row>
-    <row r="165" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K164" s="42" t="s">
+        <v>589</v>
+      </c>
+      <c r="L164" s="44" t="str">
+        <f t="shared" si="2"/>
+        <v>*P0014*</v>
+      </c>
+    </row>
+    <row r="165" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="6"/>
       <c r="B165" s="6"/>
       <c r="C165" s="26" t="s">
@@ -6235,8 +8583,15 @@
       <c r="J165" s="10">
         <v>330</v>
       </c>
-    </row>
-    <row r="166" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K165" s="42" t="s">
+        <v>590</v>
+      </c>
+      <c r="L165" s="44" t="str">
+        <f t="shared" si="2"/>
+        <v>*P0389*</v>
+      </c>
+    </row>
+    <row r="166" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="6"/>
       <c r="B166" s="6"/>
       <c r="C166" s="26" t="s">
@@ -6261,8 +8616,15 @@
       <c r="J166" s="10">
         <v>300</v>
       </c>
-    </row>
-    <row r="167" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K166" s="42" t="s">
+        <v>591</v>
+      </c>
+      <c r="L166" s="44" t="str">
+        <f t="shared" si="2"/>
+        <v>*P0374*</v>
+      </c>
+    </row>
+    <row r="167" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="6"/>
       <c r="B167" s="6"/>
       <c r="C167" s="26" t="s">
@@ -6287,8 +8649,15 @@
       <c r="J167" s="10">
         <v>230</v>
       </c>
-    </row>
-    <row r="168" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K167" s="42" t="s">
+        <v>592</v>
+      </c>
+      <c r="L167" s="44" t="str">
+        <f t="shared" si="2"/>
+        <v>*P0375*</v>
+      </c>
+    </row>
+    <row r="168" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="6"/>
       <c r="B168" s="6"/>
       <c r="C168" s="26" t="s">
@@ -6313,8 +8682,15 @@
       <c r="J168" s="10">
         <v>345</v>
       </c>
-    </row>
-    <row r="169" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K168" s="42" t="s">
+        <v>593</v>
+      </c>
+      <c r="L168" s="44" t="str">
+        <f t="shared" si="2"/>
+        <v>*P0012*</v>
+      </c>
+    </row>
+    <row r="169" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="6"/>
       <c r="B169" s="6"/>
       <c r="C169" s="26" t="s">
@@ -6339,8 +8715,15 @@
       <c r="J169" s="10">
         <v>310</v>
       </c>
-    </row>
-    <row r="170" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K169" s="42" t="s">
+        <v>594</v>
+      </c>
+      <c r="L169" s="44" t="str">
+        <f t="shared" si="2"/>
+        <v>*P0387*</v>
+      </c>
+    </row>
+    <row r="170" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="6"/>
       <c r="B170" s="6"/>
       <c r="C170" s="26" t="s">
@@ -6365,8 +8748,15 @@
       <c r="J170" s="10">
         <v>300</v>
       </c>
-    </row>
-    <row r="171" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K170" s="42" t="s">
+        <v>595</v>
+      </c>
+      <c r="L170" s="44" t="str">
+        <f t="shared" si="2"/>
+        <v>*P0376*</v>
+      </c>
+    </row>
+    <row r="171" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="6"/>
       <c r="B171" s="6"/>
       <c r="C171" s="26" t="s">
@@ -6391,8 +8781,15 @@
       <c r="J171" s="10">
         <v>345</v>
       </c>
-    </row>
-    <row r="172" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K171" s="42" t="s">
+        <v>596</v>
+      </c>
+      <c r="L171" s="44" t="str">
+        <f t="shared" si="2"/>
+        <v>*P0013*</v>
+      </c>
+    </row>
+    <row r="172" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="6"/>
       <c r="B172" s="6"/>
       <c r="C172" s="26" t="s">
@@ -6417,8 +8814,15 @@
       <c r="J172" s="10">
         <v>310</v>
       </c>
-    </row>
-    <row r="173" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K172" s="42" t="s">
+        <v>597</v>
+      </c>
+      <c r="L172" s="44" t="str">
+        <f t="shared" si="2"/>
+        <v>*P0388*</v>
+      </c>
+    </row>
+    <row r="173" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="6"/>
       <c r="B173" s="6"/>
       <c r="C173" s="26" t="s">
@@ -6443,8 +8847,15 @@
       <c r="J173" s="10">
         <v>400</v>
       </c>
-    </row>
-    <row r="174" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K173" s="42" t="s">
+        <v>598</v>
+      </c>
+      <c r="L173" s="44" t="str">
+        <f t="shared" si="2"/>
+        <v>*P0007*</v>
+      </c>
+    </row>
+    <row r="174" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="6"/>
       <c r="B174" s="6"/>
       <c r="C174" s="26" t="s">
@@ -6469,8 +8880,15 @@
       <c r="J174" s="10">
         <v>400</v>
       </c>
-    </row>
-    <row r="175" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K174" s="42" t="s">
+        <v>599</v>
+      </c>
+      <c r="L174" s="44" t="str">
+        <f t="shared" si="2"/>
+        <v>*P0315*</v>
+      </c>
+    </row>
+    <row r="175" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="6"/>
       <c r="B175" s="6"/>
       <c r="C175" s="26" t="s">
@@ -6495,8 +8913,15 @@
       <c r="J175" s="10">
         <v>450</v>
       </c>
-    </row>
-    <row r="176" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K175" s="42" t="s">
+        <v>600</v>
+      </c>
+      <c r="L175" s="44" t="str">
+        <f t="shared" si="2"/>
+        <v>*P0380*</v>
+      </c>
+    </row>
+    <row r="176" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="6"/>
       <c r="B176" s="6"/>
       <c r="C176" s="26" t="s">
@@ -6521,8 +8946,15 @@
       <c r="J176" s="10">
         <v>230</v>
       </c>
-    </row>
-    <row r="177" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K176" s="42" t="s">
+        <v>601</v>
+      </c>
+      <c r="L176" s="44" t="str">
+        <f t="shared" si="2"/>
+        <v>*P0379*</v>
+      </c>
+    </row>
+    <row r="177" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="6"/>
       <c r="B177" s="6"/>
       <c r="C177" s="26" t="s">
@@ -6547,8 +8979,15 @@
       <c r="J177" s="28">
         <v>345</v>
       </c>
-    </row>
-    <row r="178" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K177" s="42" t="s">
+        <v>602</v>
+      </c>
+      <c r="L177" s="44" t="str">
+        <f t="shared" si="2"/>
+        <v>*P0015*</v>
+      </c>
+    </row>
+    <row r="178" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="6"/>
       <c r="B178" s="6"/>
       <c r="C178" s="26" t="s">
@@ -6573,8 +9012,15 @@
       <c r="J178" s="28">
         <v>310</v>
       </c>
-    </row>
-    <row r="179" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K178" s="42" t="s">
+        <v>603</v>
+      </c>
+      <c r="L178" s="44" t="str">
+        <f t="shared" si="2"/>
+        <v>*P0390*</v>
+      </c>
+    </row>
+    <row r="179" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="6"/>
       <c r="B179" s="6"/>
       <c r="C179" s="29" t="s">
@@ -6599,8 +9045,15 @@
       <c r="J179" s="28">
         <v>200</v>
       </c>
-    </row>
-    <row r="180" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K179" s="42" t="s">
+        <v>604</v>
+      </c>
+      <c r="L179" s="44" t="str">
+        <f t="shared" si="2"/>
+        <v>*P0324*</v>
+      </c>
+    </row>
+    <row r="180" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="6"/>
       <c r="B180" s="6"/>
       <c r="C180" s="29" t="s">
@@ -6625,8 +9078,15 @@
       <c r="J180" s="28">
         <v>200</v>
       </c>
-    </row>
-    <row r="181" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K180" s="42" t="s">
+        <v>605</v>
+      </c>
+      <c r="L180" s="44" t="str">
+        <f t="shared" si="2"/>
+        <v>*P0325*</v>
+      </c>
+    </row>
+    <row r="181" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="6"/>
       <c r="B181" s="6"/>
       <c r="C181" s="29" t="s">
@@ -6651,8 +9111,15 @@
       <c r="J181" s="28">
         <v>200</v>
       </c>
-    </row>
-    <row r="182" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K181" s="42" t="s">
+        <v>606</v>
+      </c>
+      <c r="L181" s="44" t="str">
+        <f t="shared" si="2"/>
+        <v>*P0326*</v>
+      </c>
+    </row>
+    <row r="182" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="6"/>
       <c r="B182" s="6"/>
       <c r="C182" s="29" t="s">
@@ -6677,8 +9144,15 @@
       <c r="J182" s="28">
         <v>200</v>
       </c>
-    </row>
-    <row r="183" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K182" s="42" t="s">
+        <v>607</v>
+      </c>
+      <c r="L182" s="44" t="str">
+        <f t="shared" si="2"/>
+        <v>*P0327*</v>
+      </c>
+    </row>
+    <row r="183" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="6"/>
       <c r="B183" s="6"/>
       <c r="C183" s="29" t="s">
@@ -6703,8 +9177,15 @@
       <c r="J183" s="28">
         <v>200</v>
       </c>
-    </row>
-    <row r="184" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K183" s="42" t="s">
+        <v>608</v>
+      </c>
+      <c r="L183" s="44" t="str">
+        <f t="shared" si="2"/>
+        <v>*P0328*</v>
+      </c>
+    </row>
+    <row r="184" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="6"/>
       <c r="B184" s="6"/>
       <c r="C184" s="29" t="s">
@@ -6729,8 +9210,15 @@
       <c r="J184" s="28">
         <v>200</v>
       </c>
-    </row>
-    <row r="185" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K184" s="42" t="s">
+        <v>609</v>
+      </c>
+      <c r="L184" s="44" t="str">
+        <f t="shared" si="2"/>
+        <v>*P0329*</v>
+      </c>
+    </row>
+    <row r="185" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="6"/>
       <c r="B185" s="6"/>
       <c r="C185" s="29" t="s">
@@ -6755,8 +9243,15 @@
       <c r="J185" s="28">
         <v>200</v>
       </c>
-    </row>
-    <row r="186" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K185" s="42" t="s">
+        <v>610</v>
+      </c>
+      <c r="L185" s="44" t="str">
+        <f t="shared" si="2"/>
+        <v>*P0330*</v>
+      </c>
+    </row>
+    <row r="186" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="6"/>
       <c r="B186" s="6"/>
       <c r="C186" s="29" t="s">
@@ -6781,8 +9276,15 @@
       <c r="J186" s="28">
         <v>200</v>
       </c>
-    </row>
-    <row r="187" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K186" s="42" t="s">
+        <v>611</v>
+      </c>
+      <c r="L186" s="44" t="str">
+        <f t="shared" si="2"/>
+        <v>*P0331*</v>
+      </c>
+    </row>
+    <row r="187" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="6"/>
       <c r="B187" s="6"/>
       <c r="C187" s="29" t="s">
@@ -6807,8 +9309,15 @@
       <c r="J187" s="28">
         <v>200</v>
       </c>
-    </row>
-    <row r="188" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K187" s="42" t="s">
+        <v>612</v>
+      </c>
+      <c r="L187" s="44" t="str">
+        <f t="shared" si="2"/>
+        <v>*P0332*</v>
+      </c>
+    </row>
+    <row r="188" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="6"/>
       <c r="B188" s="6"/>
       <c r="C188" s="29" t="s">
@@ -6833,8 +9342,15 @@
       <c r="J188" s="28">
         <v>200</v>
       </c>
-    </row>
-    <row r="189" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K188" s="42" t="s">
+        <v>613</v>
+      </c>
+      <c r="L188" s="44" t="str">
+        <f t="shared" si="2"/>
+        <v>*P0333*</v>
+      </c>
+    </row>
+    <row r="189" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="6"/>
       <c r="B189" s="6"/>
       <c r="C189" s="29" t="s">
@@ -6859,8 +9375,15 @@
       <c r="J189" s="28">
         <v>200</v>
       </c>
-    </row>
-    <row r="190" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K189" s="42" t="s">
+        <v>614</v>
+      </c>
+      <c r="L189" s="44" t="str">
+        <f t="shared" si="2"/>
+        <v>*P0334*</v>
+      </c>
+    </row>
+    <row r="190" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="6"/>
       <c r="B190" s="6"/>
       <c r="C190" s="29" t="s">
@@ -6885,8 +9408,15 @@
       <c r="J190" s="28">
         <v>200</v>
       </c>
-    </row>
-    <row r="191" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K190" s="42" t="s">
+        <v>615</v>
+      </c>
+      <c r="L190" s="44" t="str">
+        <f t="shared" si="2"/>
+        <v>*P0335*</v>
+      </c>
+    </row>
+    <row r="191" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="6"/>
       <c r="B191" s="6"/>
       <c r="C191" s="29" t="s">
@@ -6911,8 +9441,15 @@
       <c r="J191" s="28">
         <v>200</v>
       </c>
-    </row>
-    <row r="192" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K191" s="42" t="s">
+        <v>616</v>
+      </c>
+      <c r="L191" s="44" t="str">
+        <f t="shared" si="2"/>
+        <v>*P0336*</v>
+      </c>
+    </row>
+    <row r="192" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="6"/>
       <c r="B192" s="6"/>
       <c r="C192" s="29" t="s">
@@ -6937,8 +9474,15 @@
       <c r="J192" s="28">
         <v>200</v>
       </c>
-    </row>
-    <row r="193" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K192" s="42" t="s">
+        <v>617</v>
+      </c>
+      <c r="L192" s="44" t="str">
+        <f t="shared" si="2"/>
+        <v>*P0337*</v>
+      </c>
+    </row>
+    <row r="193" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="6"/>
       <c r="B193" s="6"/>
       <c r="C193" s="29" t="s">
@@ -6963,8 +9507,15 @@
       <c r="J193" s="28">
         <v>200</v>
       </c>
-    </row>
-    <row r="194" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K193" s="42" t="s">
+        <v>618</v>
+      </c>
+      <c r="L193" s="44" t="str">
+        <f t="shared" si="2"/>
+        <v>*P0338*</v>
+      </c>
+    </row>
+    <row r="194" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="6"/>
       <c r="B194" s="6"/>
       <c r="C194" s="29" t="s">
@@ -6989,8 +9540,15 @@
       <c r="J194" s="28">
         <v>200</v>
       </c>
-    </row>
-    <row r="195" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K194" s="42" t="s">
+        <v>619</v>
+      </c>
+      <c r="L194" s="44" t="str">
+        <f t="shared" ref="L194:L257" si="3">"*"&amp;UPPER(K194)&amp;"*"</f>
+        <v>*P0339*</v>
+      </c>
+    </row>
+    <row r="195" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="6"/>
       <c r="B195" s="6"/>
       <c r="C195" s="29" t="s">
@@ -7015,8 +9573,15 @@
       <c r="J195" s="28">
         <v>200</v>
       </c>
-    </row>
-    <row r="196" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K195" s="42" t="s">
+        <v>620</v>
+      </c>
+      <c r="L195" s="44" t="str">
+        <f t="shared" si="3"/>
+        <v>*P0340*</v>
+      </c>
+    </row>
+    <row r="196" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="6"/>
       <c r="B196" s="6"/>
       <c r="C196" s="29" t="s">
@@ -7041,8 +9606,15 @@
       <c r="J196" s="28">
         <v>200</v>
       </c>
-    </row>
-    <row r="197" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K196" s="42" t="s">
+        <v>621</v>
+      </c>
+      <c r="L196" s="44" t="str">
+        <f t="shared" si="3"/>
+        <v>*P0341*</v>
+      </c>
+    </row>
+    <row r="197" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="6"/>
       <c r="B197" s="6"/>
       <c r="C197" s="29" t="s">
@@ -7067,8 +9639,15 @@
       <c r="J197" s="28">
         <v>200</v>
       </c>
-    </row>
-    <row r="198" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K197" s="42" t="s">
+        <v>622</v>
+      </c>
+      <c r="L197" s="44" t="str">
+        <f t="shared" si="3"/>
+        <v>*P0342*</v>
+      </c>
+    </row>
+    <row r="198" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="6"/>
       <c r="B198" s="6"/>
       <c r="C198" s="29" t="s">
@@ -7093,8 +9672,15 @@
       <c r="J198" s="28">
         <v>200</v>
       </c>
-    </row>
-    <row r="199" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K198" s="42" t="s">
+        <v>623</v>
+      </c>
+      <c r="L198" s="44" t="str">
+        <f t="shared" si="3"/>
+        <v>*P0346*</v>
+      </c>
+    </row>
+    <row r="199" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="6"/>
       <c r="B199" s="6"/>
       <c r="C199" s="29" t="s">
@@ -7119,8 +9705,15 @@
       <c r="J199" s="28">
         <v>200</v>
       </c>
-    </row>
-    <row r="200" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K199" s="42" t="s">
+        <v>624</v>
+      </c>
+      <c r="L199" s="44" t="str">
+        <f t="shared" si="3"/>
+        <v>*P0347*</v>
+      </c>
+    </row>
+    <row r="200" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="6"/>
       <c r="B200" s="6"/>
       <c r="C200" s="29" t="s">
@@ -7145,8 +9738,15 @@
       <c r="J200" s="28">
         <v>200</v>
       </c>
-    </row>
-    <row r="201" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K200" s="42" t="s">
+        <v>625</v>
+      </c>
+      <c r="L200" s="44" t="str">
+        <f t="shared" si="3"/>
+        <v>*P0348*</v>
+      </c>
+    </row>
+    <row r="201" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="6"/>
       <c r="B201" s="6"/>
       <c r="C201" s="29" t="s">
@@ -7171,8 +9771,15 @@
       <c r="J201" s="28">
         <v>200</v>
       </c>
-    </row>
-    <row r="202" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K201" s="42" t="s">
+        <v>626</v>
+      </c>
+      <c r="L201" s="44" t="str">
+        <f t="shared" si="3"/>
+        <v>*P0349*</v>
+      </c>
+    </row>
+    <row r="202" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="6"/>
       <c r="B202" s="6"/>
       <c r="C202" s="29" t="s">
@@ -7197,8 +9804,15 @@
       <c r="J202" s="28">
         <v>200</v>
       </c>
-    </row>
-    <row r="203" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K202" s="42" t="s">
+        <v>627</v>
+      </c>
+      <c r="L202" s="44" t="str">
+        <f t="shared" si="3"/>
+        <v>*P0350*</v>
+      </c>
+    </row>
+    <row r="203" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="6"/>
       <c r="B203" s="6"/>
       <c r="C203" s="29" t="s">
@@ -7223,8 +9837,15 @@
       <c r="J203" s="28">
         <v>200</v>
       </c>
-    </row>
-    <row r="204" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K203" s="42" t="s">
+        <v>628</v>
+      </c>
+      <c r="L203" s="44" t="str">
+        <f t="shared" si="3"/>
+        <v>*P0351*</v>
+      </c>
+    </row>
+    <row r="204" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="6"/>
       <c r="B204" s="6"/>
       <c r="C204" s="29" t="s">
@@ -7249,8 +9870,15 @@
       <c r="J204" s="28">
         <v>250</v>
       </c>
-    </row>
-    <row r="205" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K204" s="42" t="s">
+        <v>629</v>
+      </c>
+      <c r="L204" s="44" t="str">
+        <f t="shared" si="3"/>
+        <v>*P0343*</v>
+      </c>
+    </row>
+    <row r="205" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="6"/>
       <c r="B205" s="6"/>
       <c r="C205" s="29" t="s">
@@ -7275,8 +9903,15 @@
       <c r="J205" s="28">
         <v>250</v>
       </c>
-    </row>
-    <row r="206" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K205" s="42" t="s">
+        <v>630</v>
+      </c>
+      <c r="L205" s="44" t="str">
+        <f t="shared" si="3"/>
+        <v>*P0344*</v>
+      </c>
+    </row>
+    <row r="206" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="6"/>
       <c r="B206" s="6"/>
       <c r="C206" s="29" t="s">
@@ -7301,8 +9936,15 @@
       <c r="J206" s="28">
         <v>250</v>
       </c>
-    </row>
-    <row r="207" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K206" s="42" t="s">
+        <v>631</v>
+      </c>
+      <c r="L206" s="44" t="str">
+        <f t="shared" si="3"/>
+        <v>*P0345*</v>
+      </c>
+    </row>
+    <row r="207" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="6"/>
       <c r="B207" s="6"/>
       <c r="C207" s="31" t="s">
@@ -7327,8 +9969,15 @@
       <c r="J207" s="28">
         <v>320</v>
       </c>
-    </row>
-    <row r="208" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K207" s="42" t="s">
+        <v>632</v>
+      </c>
+      <c r="L207" s="44" t="str">
+        <f t="shared" si="3"/>
+        <v>*P0322*</v>
+      </c>
+    </row>
+    <row r="208" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="6"/>
       <c r="B208" s="6"/>
       <c r="C208" s="31" t="s">
@@ -7353,8 +10002,15 @@
       <c r="J208" s="28">
         <v>250</v>
       </c>
-    </row>
-    <row r="209" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K208" s="42" t="s">
+        <v>633</v>
+      </c>
+      <c r="L208" s="44" t="str">
+        <f t="shared" si="3"/>
+        <v>*P0320*</v>
+      </c>
+    </row>
+    <row r="209" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="6"/>
       <c r="B209" s="6"/>
       <c r="C209" s="31" t="s">
@@ -7379,8 +10035,15 @@
       <c r="J209" s="28">
         <v>200</v>
       </c>
-    </row>
-    <row r="210" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K209" s="42" t="s">
+        <v>634</v>
+      </c>
+      <c r="L209" s="44" t="str">
+        <f t="shared" si="3"/>
+        <v>*P0321*</v>
+      </c>
+    </row>
+    <row r="210" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="6"/>
       <c r="B210" s="6"/>
       <c r="C210" s="33" t="s">
@@ -7401,8 +10064,15 @@
       <c r="J210" s="28">
         <v>85</v>
       </c>
-    </row>
-    <row r="211" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K210" s="42" t="s">
+        <v>635</v>
+      </c>
+      <c r="L210" s="44" t="str">
+        <f t="shared" si="3"/>
+        <v>*P0147*</v>
+      </c>
+    </row>
+    <row r="211" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="6"/>
       <c r="B211" s="6"/>
       <c r="C211" s="33" t="s">
@@ -7423,8 +10093,15 @@
       <c r="J211" s="28">
         <v>85</v>
       </c>
-    </row>
-    <row r="212" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K211" s="42" t="s">
+        <v>636</v>
+      </c>
+      <c r="L211" s="44" t="str">
+        <f t="shared" si="3"/>
+        <v>*P0139*</v>
+      </c>
+    </row>
+    <row r="212" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="6"/>
       <c r="B212" s="6"/>
       <c r="C212" s="33" t="s">
@@ -7445,8 +10122,15 @@
       <c r="J212" s="28">
         <v>85</v>
       </c>
-    </row>
-    <row r="213" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K212" s="42" t="s">
+        <v>637</v>
+      </c>
+      <c r="L212" s="44" t="str">
+        <f t="shared" si="3"/>
+        <v>*P0144*</v>
+      </c>
+    </row>
+    <row r="213" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="6"/>
       <c r="B213" s="6"/>
       <c r="C213" s="33" t="s">
@@ -7467,8 +10151,15 @@
       <c r="J213" s="28">
         <v>85</v>
       </c>
-    </row>
-    <row r="214" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K213" s="42" t="s">
+        <v>638</v>
+      </c>
+      <c r="L213" s="44" t="str">
+        <f t="shared" si="3"/>
+        <v>*P0145*</v>
+      </c>
+    </row>
+    <row r="214" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="6"/>
       <c r="B214" s="6"/>
       <c r="C214" s="33" t="s">
@@ -7489,8 +10180,15 @@
       <c r="J214" s="28">
         <v>85</v>
       </c>
-    </row>
-    <row r="215" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K214" s="42" t="s">
+        <v>639</v>
+      </c>
+      <c r="L214" s="44" t="str">
+        <f t="shared" si="3"/>
+        <v>*P0140*</v>
+      </c>
+    </row>
+    <row r="215" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="6"/>
       <c r="B215" s="6"/>
       <c r="C215" s="33" t="s">
@@ -7511,8 +10209,15 @@
       <c r="J215" s="28">
         <v>85</v>
       </c>
-    </row>
-    <row r="216" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K215" s="42" t="s">
+        <v>640</v>
+      </c>
+      <c r="L215" s="44" t="str">
+        <f t="shared" si="3"/>
+        <v>*P0142*</v>
+      </c>
+    </row>
+    <row r="216" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="6"/>
       <c r="B216" s="6"/>
       <c r="C216" s="33" t="s">
@@ -7533,8 +10238,15 @@
       <c r="J216" s="28">
         <v>85</v>
       </c>
-    </row>
-    <row r="217" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K216" s="42" t="s">
+        <v>641</v>
+      </c>
+      <c r="L216" s="44" t="str">
+        <f t="shared" si="3"/>
+        <v>*P0148*</v>
+      </c>
+    </row>
+    <row r="217" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="6"/>
       <c r="B217" s="6"/>
       <c r="C217" s="33" t="s">
@@ -7555,8 +10267,15 @@
       <c r="J217" s="28">
         <v>85</v>
       </c>
-    </row>
-    <row r="218" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K217" s="42" t="s">
+        <v>642</v>
+      </c>
+      <c r="L217" s="44" t="str">
+        <f t="shared" si="3"/>
+        <v>*P0146*</v>
+      </c>
+    </row>
+    <row r="218" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="6"/>
       <c r="B218" s="6"/>
       <c r="C218" s="33" t="s">
@@ -7577,8 +10296,15 @@
       <c r="J218" s="28">
         <v>85</v>
       </c>
-    </row>
-    <row r="219" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K218" s="42" t="s">
+        <v>643</v>
+      </c>
+      <c r="L218" s="44" t="str">
+        <f t="shared" si="3"/>
+        <v>*P0143*</v>
+      </c>
+    </row>
+    <row r="219" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="6"/>
       <c r="B219" s="6"/>
       <c r="C219" s="33" t="s">
@@ -7599,8 +10325,15 @@
       <c r="J219" s="28">
         <v>85</v>
       </c>
-    </row>
-    <row r="220" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K219" s="42" t="s">
+        <v>644</v>
+      </c>
+      <c r="L219" s="44" t="str">
+        <f t="shared" si="3"/>
+        <v>*P0141*</v>
+      </c>
+    </row>
+    <row r="220" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="6"/>
       <c r="B220" s="6"/>
       <c r="C220" s="33" t="s">
@@ -7621,8 +10354,15 @@
       <c r="J220" s="28">
         <v>80</v>
       </c>
-    </row>
-    <row r="221" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K220" s="42" t="s">
+        <v>645</v>
+      </c>
+      <c r="L220" s="44" t="str">
+        <f t="shared" si="3"/>
+        <v>*P0182*</v>
+      </c>
+    </row>
+    <row r="221" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="6"/>
       <c r="B221" s="6"/>
       <c r="C221" s="33" t="s">
@@ -7643,8 +10383,15 @@
       <c r="J221" s="28">
         <v>80</v>
       </c>
-    </row>
-    <row r="222" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K221" s="42" t="s">
+        <v>646</v>
+      </c>
+      <c r="L221" s="44" t="str">
+        <f t="shared" si="3"/>
+        <v>*P0184*</v>
+      </c>
+    </row>
+    <row r="222" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="6"/>
       <c r="B222" s="6"/>
       <c r="C222" s="33" t="s">
@@ -7665,8 +10412,15 @@
       <c r="J222" s="28">
         <v>80</v>
       </c>
-    </row>
-    <row r="223" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K222" s="42" t="s">
+        <v>647</v>
+      </c>
+      <c r="L222" s="44" t="str">
+        <f t="shared" si="3"/>
+        <v>*P0183*</v>
+      </c>
+    </row>
+    <row r="223" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="6"/>
       <c r="B223" s="6"/>
       <c r="C223" s="33" t="s">
@@ -7687,8 +10441,15 @@
       <c r="J223" s="28">
         <v>80</v>
       </c>
-    </row>
-    <row r="224" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K223" s="42" t="s">
+        <v>648</v>
+      </c>
+      <c r="L223" s="44" t="str">
+        <f t="shared" si="3"/>
+        <v>*P0185*</v>
+      </c>
+    </row>
+    <row r="224" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="6"/>
       <c r="B224" s="6"/>
       <c r="C224" s="33" t="s">
@@ -7709,8 +10470,15 @@
       <c r="J224" s="28">
         <v>75</v>
       </c>
-    </row>
-    <row r="225" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K224" s="42" t="s">
+        <v>649</v>
+      </c>
+      <c r="L224" s="44" t="str">
+        <f t="shared" si="3"/>
+        <v>*P0186*</v>
+      </c>
+    </row>
+    <row r="225" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="6"/>
       <c r="B225" s="6"/>
       <c r="C225" s="33" t="s">
@@ -7731,8 +10499,15 @@
       <c r="J225" s="28">
         <v>80</v>
       </c>
-    </row>
-    <row r="226" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K225" s="42" t="s">
+        <v>650</v>
+      </c>
+      <c r="L225" s="44" t="str">
+        <f t="shared" si="3"/>
+        <v>*P0187*</v>
+      </c>
+    </row>
+    <row r="226" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="6"/>
       <c r="B226" s="6"/>
       <c r="C226" s="33" t="s">
@@ -7753,8 +10528,15 @@
       <c r="J226" s="28">
         <v>80</v>
       </c>
-    </row>
-    <row r="227" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K226" s="42" t="s">
+        <v>651</v>
+      </c>
+      <c r="L226" s="44" t="str">
+        <f t="shared" si="3"/>
+        <v>*P0188*</v>
+      </c>
+    </row>
+    <row r="227" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="6"/>
       <c r="B227" s="6"/>
       <c r="C227" s="33" t="s">
@@ -7775,8 +10557,15 @@
       <c r="J227" s="28">
         <v>80</v>
       </c>
-    </row>
-    <row r="228" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K227" s="42" t="s">
+        <v>652</v>
+      </c>
+      <c r="L227" s="44" t="str">
+        <f t="shared" si="3"/>
+        <v>*P0104*</v>
+      </c>
+    </row>
+    <row r="228" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="6"/>
       <c r="B228" s="6"/>
       <c r="C228" s="33" t="s">
@@ -7797,8 +10586,15 @@
       <c r="J228" s="28">
         <v>75</v>
       </c>
-    </row>
-    <row r="229" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K228" s="42" t="s">
+        <v>653</v>
+      </c>
+      <c r="L228" s="44" t="str">
+        <f t="shared" si="3"/>
+        <v>*P0189*</v>
+      </c>
+    </row>
+    <row r="229" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" s="6"/>
       <c r="B229" s="6"/>
       <c r="C229" s="33" t="s">
@@ -7819,8 +10615,15 @@
       <c r="J229" s="28">
         <v>80</v>
       </c>
-    </row>
-    <row r="230" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K229" s="42" t="s">
+        <v>654</v>
+      </c>
+      <c r="L229" s="44" t="str">
+        <f t="shared" si="3"/>
+        <v>*P0190*</v>
+      </c>
+    </row>
+    <row r="230" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="6"/>
       <c r="B230" s="6"/>
       <c r="C230" s="33" t="s">
@@ -7841,8 +10644,15 @@
       <c r="J230" s="28">
         <v>80</v>
       </c>
-    </row>
-    <row r="231" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K230" s="42" t="s">
+        <v>655</v>
+      </c>
+      <c r="L230" s="44" t="str">
+        <f t="shared" si="3"/>
+        <v>*P0191*</v>
+      </c>
+    </row>
+    <row r="231" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" s="6"/>
       <c r="B231" s="6"/>
       <c r="C231" s="33" t="s">
@@ -7863,8 +10673,15 @@
       <c r="J231" s="28">
         <v>75</v>
       </c>
-    </row>
-    <row r="232" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K231" s="42" t="s">
+        <v>656</v>
+      </c>
+      <c r="L231" s="44" t="str">
+        <f t="shared" si="3"/>
+        <v>*P0192*</v>
+      </c>
+    </row>
+    <row r="232" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="6"/>
       <c r="B232" s="6"/>
       <c r="C232" s="33" t="s">
@@ -7885,8 +10702,15 @@
       <c r="J232" s="28">
         <v>80</v>
       </c>
-    </row>
-    <row r="233" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K232" s="42" t="s">
+        <v>657</v>
+      </c>
+      <c r="L232" s="44" t="str">
+        <f t="shared" si="3"/>
+        <v>*P0193*</v>
+      </c>
+    </row>
+    <row r="233" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="6"/>
       <c r="B233" s="6"/>
       <c r="C233" s="33" t="s">
@@ -7907,8 +10731,15 @@
       <c r="J233" s="28">
         <v>75</v>
       </c>
-    </row>
-    <row r="234" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K233" s="42" t="s">
+        <v>658</v>
+      </c>
+      <c r="L233" s="44" t="str">
+        <f t="shared" si="3"/>
+        <v>*P0194*</v>
+      </c>
+    </row>
+    <row r="234" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="6"/>
       <c r="B234" s="6"/>
       <c r="C234" s="33" t="s">
@@ -7929,8 +10760,15 @@
       <c r="J234" s="28">
         <v>80</v>
       </c>
-    </row>
-    <row r="235" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K234" s="42" t="s">
+        <v>659</v>
+      </c>
+      <c r="L234" s="44" t="str">
+        <f t="shared" si="3"/>
+        <v>*P0196*</v>
+      </c>
+    </row>
+    <row r="235" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="6"/>
       <c r="B235" s="6"/>
       <c r="C235" s="33" t="s">
@@ -7951,8 +10789,15 @@
       <c r="J235" s="28">
         <v>80</v>
       </c>
-    </row>
-    <row r="236" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K235" s="42" t="s">
+        <v>660</v>
+      </c>
+      <c r="L235" s="44" t="str">
+        <f t="shared" si="3"/>
+        <v>*P0198*</v>
+      </c>
+    </row>
+    <row r="236" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="6"/>
       <c r="B236" s="6"/>
       <c r="C236" s="33" t="s">
@@ -7973,8 +10818,15 @@
       <c r="J236" s="28">
         <v>80</v>
       </c>
-    </row>
-    <row r="237" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K236" s="42" t="s">
+        <v>661</v>
+      </c>
+      <c r="L236" s="44" t="str">
+        <f t="shared" si="3"/>
+        <v>*P0197*</v>
+      </c>
+    </row>
+    <row r="237" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="6"/>
       <c r="B237" s="6"/>
       <c r="C237" s="33" t="s">
@@ -7995,8 +10847,15 @@
       <c r="J237" s="28">
         <v>80</v>
       </c>
-    </row>
-    <row r="238" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K237" s="42" t="s">
+        <v>662</v>
+      </c>
+      <c r="L237" s="44" t="str">
+        <f t="shared" si="3"/>
+        <v>*P0195*</v>
+      </c>
+    </row>
+    <row r="238" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="6"/>
       <c r="B238" s="6"/>
       <c r="C238" s="33" t="s">
@@ -8017,8 +10876,15 @@
       <c r="J238" s="28">
         <v>80</v>
       </c>
-    </row>
-    <row r="239" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K238" s="42" t="s">
+        <v>663</v>
+      </c>
+      <c r="L238" s="44" t="str">
+        <f t="shared" si="3"/>
+        <v>*P0199*</v>
+      </c>
+    </row>
+    <row r="239" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" s="6"/>
       <c r="B239" s="6"/>
       <c r="C239" s="33" t="s">
@@ -8039,8 +10905,15 @@
       <c r="J239" s="28">
         <v>75</v>
       </c>
-    </row>
-    <row r="240" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K239" s="42" t="s">
+        <v>664</v>
+      </c>
+      <c r="L239" s="44" t="str">
+        <f t="shared" si="3"/>
+        <v>*P0200*</v>
+      </c>
+    </row>
+    <row r="240" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="6"/>
       <c r="B240" s="6"/>
       <c r="C240" s="33" t="s">
@@ -8061,8 +10934,15 @@
       <c r="J240" s="28">
         <v>80</v>
       </c>
-    </row>
-    <row r="241" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K240" s="42" t="s">
+        <v>665</v>
+      </c>
+      <c r="L240" s="44" t="str">
+        <f t="shared" si="3"/>
+        <v>*P0201*</v>
+      </c>
+    </row>
+    <row r="241" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="6"/>
       <c r="B241" s="6"/>
       <c r="C241" s="33" t="s">
@@ -8083,8 +10963,15 @@
       <c r="J241" s="28">
         <v>80</v>
       </c>
-    </row>
-    <row r="242" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K241" s="42" t="s">
+        <v>666</v>
+      </c>
+      <c r="L241" s="44" t="str">
+        <f t="shared" si="3"/>
+        <v>*P0202*</v>
+      </c>
+    </row>
+    <row r="242" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="6"/>
       <c r="B242" s="6"/>
       <c r="C242" s="33" t="s">
@@ -8105,8 +10992,15 @@
       <c r="J242" s="28">
         <v>80</v>
       </c>
-    </row>
-    <row r="243" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K242" s="42" t="s">
+        <v>667</v>
+      </c>
+      <c r="L242" s="44" t="str">
+        <f t="shared" si="3"/>
+        <v>*P0154*</v>
+      </c>
+    </row>
+    <row r="243" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" s="6"/>
       <c r="B243" s="6"/>
       <c r="C243" s="33" t="s">
@@ -8127,8 +11021,15 @@
       <c r="J243" s="28">
         <v>80</v>
       </c>
-    </row>
-    <row r="244" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K243" s="42" t="s">
+        <v>668</v>
+      </c>
+      <c r="L243" s="44" t="str">
+        <f t="shared" si="3"/>
+        <v>*P0155*</v>
+      </c>
+    </row>
+    <row r="244" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" s="6"/>
       <c r="B244" s="6"/>
       <c r="C244" s="33" t="s">
@@ -8149,8 +11050,15 @@
       <c r="J244" s="28">
         <v>80</v>
       </c>
-    </row>
-    <row r="245" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K244" s="42" t="s">
+        <v>669</v>
+      </c>
+      <c r="L244" s="44" t="str">
+        <f t="shared" si="3"/>
+        <v>*P0156*</v>
+      </c>
+    </row>
+    <row r="245" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" s="6"/>
       <c r="B245" s="6"/>
       <c r="C245" s="33" t="s">
@@ -8171,8 +11079,15 @@
       <c r="J245" s="28">
         <v>80</v>
       </c>
-    </row>
-    <row r="246" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K245" s="42" t="s">
+        <v>670</v>
+      </c>
+      <c r="L245" s="44" t="str">
+        <f t="shared" si="3"/>
+        <v>*P0157*</v>
+      </c>
+    </row>
+    <row r="246" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" s="6"/>
       <c r="B246" s="6"/>
       <c r="C246" s="33" t="s">
@@ -8193,8 +11108,15 @@
       <c r="J246" s="28">
         <v>80</v>
       </c>
-    </row>
-    <row r="247" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K246" s="42" t="s">
+        <v>671</v>
+      </c>
+      <c r="L246" s="44" t="str">
+        <f t="shared" si="3"/>
+        <v>*P0158*</v>
+      </c>
+    </row>
+    <row r="247" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" s="6"/>
       <c r="B247" s="6"/>
       <c r="C247" s="33" t="s">
@@ -8215,8 +11137,15 @@
       <c r="J247" s="28">
         <v>75</v>
       </c>
-    </row>
-    <row r="248" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K247" s="42" t="s">
+        <v>672</v>
+      </c>
+      <c r="L247" s="44" t="str">
+        <f t="shared" si="3"/>
+        <v>*P0159*</v>
+      </c>
+    </row>
+    <row r="248" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" s="6"/>
       <c r="B248" s="6"/>
       <c r="C248" s="33" t="s">
@@ -8237,8 +11166,15 @@
       <c r="J248" s="28">
         <v>75</v>
       </c>
-    </row>
-    <row r="249" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K248" s="42" t="s">
+        <v>673</v>
+      </c>
+      <c r="L248" s="44" t="str">
+        <f t="shared" si="3"/>
+        <v>*P0160*</v>
+      </c>
+    </row>
+    <row r="249" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249" s="6"/>
       <c r="B249" s="6"/>
       <c r="C249" s="33" t="s">
@@ -8259,8 +11195,15 @@
       <c r="J249" s="28">
         <v>80</v>
       </c>
-    </row>
-    <row r="250" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K249" s="42" t="s">
+        <v>674</v>
+      </c>
+      <c r="L249" s="44" t="str">
+        <f t="shared" si="3"/>
+        <v>*P0161*</v>
+      </c>
+    </row>
+    <row r="250" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" s="6"/>
       <c r="B250" s="6"/>
       <c r="C250" s="33" t="s">
@@ -8281,8 +11224,15 @@
       <c r="J250" s="28">
         <v>80</v>
       </c>
-    </row>
-    <row r="251" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K250" s="42" t="s">
+        <v>675</v>
+      </c>
+      <c r="L250" s="44" t="str">
+        <f t="shared" si="3"/>
+        <v>*P0162*</v>
+      </c>
+    </row>
+    <row r="251" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" s="6"/>
       <c r="B251" s="6"/>
       <c r="C251" s="33" t="s">
@@ -8303,8 +11253,15 @@
       <c r="J251" s="28">
         <v>80</v>
       </c>
-    </row>
-    <row r="252" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K251" s="42" t="s">
+        <v>676</v>
+      </c>
+      <c r="L251" s="44" t="str">
+        <f t="shared" si="3"/>
+        <v>*P0163*</v>
+      </c>
+    </row>
+    <row r="252" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" s="6"/>
       <c r="B252" s="6"/>
       <c r="C252" s="33" t="s">
@@ -8325,8 +11282,15 @@
       <c r="J252" s="28">
         <v>80</v>
       </c>
-    </row>
-    <row r="253" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K252" s="42" t="s">
+        <v>677</v>
+      </c>
+      <c r="L252" s="44" t="str">
+        <f t="shared" si="3"/>
+        <v>*P0164*</v>
+      </c>
+    </row>
+    <row r="253" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253" s="6"/>
       <c r="B253" s="6"/>
       <c r="C253" s="33" t="s">
@@ -8347,8 +11311,15 @@
       <c r="J253" s="28">
         <v>80</v>
       </c>
-    </row>
-    <row r="254" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K253" s="42" t="s">
+        <v>678</v>
+      </c>
+      <c r="L253" s="44" t="str">
+        <f t="shared" si="3"/>
+        <v>*P0165*</v>
+      </c>
+    </row>
+    <row r="254" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" s="6"/>
       <c r="B254" s="6"/>
       <c r="C254" s="33" t="s">
@@ -8369,8 +11340,15 @@
       <c r="J254" s="28">
         <v>80</v>
       </c>
-    </row>
-    <row r="255" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K254" s="42" t="s">
+        <v>679</v>
+      </c>
+      <c r="L254" s="44" t="str">
+        <f t="shared" si="3"/>
+        <v>*P0166*</v>
+      </c>
+    </row>
+    <row r="255" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="6"/>
       <c r="B255" s="6"/>
       <c r="C255" s="33" t="s">
@@ -8391,8 +11369,15 @@
       <c r="J255" s="28">
         <v>75</v>
       </c>
-    </row>
-    <row r="256" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K255" s="42" t="s">
+        <v>680</v>
+      </c>
+      <c r="L255" s="44" t="str">
+        <f t="shared" si="3"/>
+        <v>*P0167*</v>
+      </c>
+    </row>
+    <row r="256" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" s="6"/>
       <c r="B256" s="6"/>
       <c r="C256" s="33" t="s">
@@ -8413,8 +11398,15 @@
       <c r="J256" s="28">
         <v>75</v>
       </c>
-    </row>
-    <row r="257" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K256" s="42" t="s">
+        <v>681</v>
+      </c>
+      <c r="L256" s="44" t="str">
+        <f t="shared" si="3"/>
+        <v>*P0168*</v>
+      </c>
+    </row>
+    <row r="257" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257" s="6"/>
       <c r="B257" s="6"/>
       <c r="C257" s="33" t="s">
@@ -8435,8 +11427,15 @@
       <c r="J257" s="28">
         <v>75</v>
       </c>
-    </row>
-    <row r="258" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K257" s="42" t="s">
+        <v>682</v>
+      </c>
+      <c r="L257" s="44" t="str">
+        <f t="shared" si="3"/>
+        <v>*P0169*</v>
+      </c>
+    </row>
+    <row r="258" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" s="6"/>
       <c r="B258" s="6"/>
       <c r="C258" s="33" t="s">
@@ -8457,8 +11456,15 @@
       <c r="J258" s="28">
         <v>75</v>
       </c>
-    </row>
-    <row r="259" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K258" s="42" t="s">
+        <v>683</v>
+      </c>
+      <c r="L258" s="44" t="str">
+        <f t="shared" ref="L258:L321" si="4">"*"&amp;UPPER(K258)&amp;"*"</f>
+        <v>*P0170*</v>
+      </c>
+    </row>
+    <row r="259" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259" s="6"/>
       <c r="B259" s="6"/>
       <c r="C259" s="33" t="s">
@@ -8479,8 +11485,15 @@
       <c r="J259" s="28">
         <v>80</v>
       </c>
-    </row>
-    <row r="260" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K259" s="42" t="s">
+        <v>684</v>
+      </c>
+      <c r="L259" s="44" t="str">
+        <f t="shared" si="4"/>
+        <v>*P0171*</v>
+      </c>
+    </row>
+    <row r="260" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260" s="6"/>
       <c r="B260" s="6"/>
       <c r="C260" s="33" t="s">
@@ -8501,8 +11514,15 @@
       <c r="J260" s="28">
         <v>80</v>
       </c>
-    </row>
-    <row r="261" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K260" s="42" t="s">
+        <v>685</v>
+      </c>
+      <c r="L260" s="44" t="str">
+        <f t="shared" si="4"/>
+        <v>*P0181*</v>
+      </c>
+    </row>
+    <row r="261" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261" s="6"/>
       <c r="B261" s="6"/>
       <c r="C261" s="33" t="s">
@@ -8523,8 +11543,15 @@
       <c r="J261" s="28">
         <v>80</v>
       </c>
-    </row>
-    <row r="262" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K261" s="42" t="s">
+        <v>686</v>
+      </c>
+      <c r="L261" s="44" t="str">
+        <f t="shared" si="4"/>
+        <v>*P0172*</v>
+      </c>
+    </row>
+    <row r="262" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" s="6"/>
       <c r="B262" s="6"/>
       <c r="C262" s="33" t="s">
@@ -8545,8 +11572,15 @@
       <c r="J262" s="28">
         <v>80</v>
       </c>
-    </row>
-    <row r="263" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K262" s="42" t="s">
+        <v>687</v>
+      </c>
+      <c r="L262" s="44" t="str">
+        <f t="shared" si="4"/>
+        <v>*P0174*</v>
+      </c>
+    </row>
+    <row r="263" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263" s="6"/>
       <c r="B263" s="6"/>
       <c r="C263" s="33" t="s">
@@ -8567,8 +11601,15 @@
       <c r="J263" s="28">
         <v>80</v>
       </c>
-    </row>
-    <row r="264" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K263" s="42" t="s">
+        <v>688</v>
+      </c>
+      <c r="L263" s="44" t="str">
+        <f t="shared" si="4"/>
+        <v>*P0173*</v>
+      </c>
+    </row>
+    <row r="264" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" s="6"/>
       <c r="B264" s="6"/>
       <c r="C264" s="33" t="s">
@@ -8589,8 +11630,15 @@
       <c r="J264" s="28">
         <v>80</v>
       </c>
-    </row>
-    <row r="265" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K264" s="42" t="s">
+        <v>689</v>
+      </c>
+      <c r="L264" s="44" t="str">
+        <f t="shared" si="4"/>
+        <v>*P0175*</v>
+      </c>
+    </row>
+    <row r="265" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" s="6"/>
       <c r="B265" s="6"/>
       <c r="C265" s="33" t="s">
@@ -8611,8 +11659,15 @@
       <c r="J265" s="28">
         <v>80</v>
       </c>
-    </row>
-    <row r="266" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K265" s="42" t="s">
+        <v>690</v>
+      </c>
+      <c r="L265" s="44" t="str">
+        <f t="shared" si="4"/>
+        <v>*P0176*</v>
+      </c>
+    </row>
+    <row r="266" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266" s="6"/>
       <c r="B266" s="6"/>
       <c r="C266" s="33" t="s">
@@ -8633,8 +11688,15 @@
       <c r="J266" s="28">
         <v>75</v>
       </c>
-    </row>
-    <row r="267" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K266" s="42" t="s">
+        <v>691</v>
+      </c>
+      <c r="L266" s="44" t="str">
+        <f t="shared" si="4"/>
+        <v>*P0177*</v>
+      </c>
+    </row>
+    <row r="267" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" s="6"/>
       <c r="B267" s="6"/>
       <c r="C267" s="33" t="s">
@@ -8655,8 +11717,15 @@
       <c r="J267" s="28">
         <v>80</v>
       </c>
-    </row>
-    <row r="268" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K267" s="42" t="s">
+        <v>692</v>
+      </c>
+      <c r="L267" s="44" t="str">
+        <f t="shared" si="4"/>
+        <v>*P0178*</v>
+      </c>
+    </row>
+    <row r="268" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="6"/>
       <c r="B268" s="6"/>
       <c r="C268" s="33" t="s">
@@ -8677,8 +11746,15 @@
       <c r="J268" s="28">
         <v>80</v>
       </c>
-    </row>
-    <row r="269" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K268" s="42" t="s">
+        <v>693</v>
+      </c>
+      <c r="L268" s="44" t="str">
+        <f t="shared" si="4"/>
+        <v>*P0179*</v>
+      </c>
+    </row>
+    <row r="269" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269" s="6"/>
       <c r="B269" s="6"/>
       <c r="C269" s="33" t="s">
@@ -8699,8 +11775,15 @@
       <c r="J269" s="28">
         <v>80</v>
       </c>
-    </row>
-    <row r="270" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K269" s="42" t="s">
+        <v>694</v>
+      </c>
+      <c r="L269" s="44" t="str">
+        <f t="shared" si="4"/>
+        <v>*P0180*</v>
+      </c>
+    </row>
+    <row r="270" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270" s="6"/>
       <c r="B270" s="6"/>
       <c r="C270" s="33" t="s">
@@ -8721,8 +11804,15 @@
       <c r="J270" s="28">
         <v>165</v>
       </c>
-    </row>
-    <row r="271" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K270" s="42" t="s">
+        <v>695</v>
+      </c>
+      <c r="L270" s="44" t="str">
+        <f t="shared" si="4"/>
+        <v>*P0211*</v>
+      </c>
+    </row>
+    <row r="271" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271" s="6"/>
       <c r="B271" s="6"/>
       <c r="C271" s="33" t="s">
@@ -8743,8 +11833,15 @@
       <c r="J271" s="28">
         <v>165</v>
       </c>
-    </row>
-    <row r="272" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K271" s="42" t="s">
+        <v>696</v>
+      </c>
+      <c r="L271" s="44" t="str">
+        <f t="shared" si="4"/>
+        <v>*P0207*</v>
+      </c>
+    </row>
+    <row r="272" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A272" s="6"/>
       <c r="B272" s="6"/>
       <c r="C272" s="33" t="s">
@@ -8765,8 +11862,15 @@
       <c r="J272" s="28">
         <v>165</v>
       </c>
-    </row>
-    <row r="273" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K272" s="42" t="s">
+        <v>697</v>
+      </c>
+      <c r="L272" s="44" t="str">
+        <f t="shared" si="4"/>
+        <v>*P0209*</v>
+      </c>
+    </row>
+    <row r="273" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273" s="6"/>
       <c r="B273" s="6"/>
       <c r="C273" s="33" t="s">
@@ -8787,8 +11891,15 @@
       <c r="J273" s="28">
         <v>165</v>
       </c>
-    </row>
-    <row r="274" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K273" s="42" t="s">
+        <v>698</v>
+      </c>
+      <c r="L273" s="44" t="str">
+        <f t="shared" si="4"/>
+        <v>*P0212*</v>
+      </c>
+    </row>
+    <row r="274" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="6"/>
       <c r="B274" s="6"/>
       <c r="C274" s="33" t="s">
@@ -8809,8 +11920,15 @@
       <c r="J274" s="28">
         <v>165</v>
       </c>
-    </row>
-    <row r="275" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K274" s="42" t="s">
+        <v>699</v>
+      </c>
+      <c r="L274" s="44" t="str">
+        <f t="shared" si="4"/>
+        <v>*P0214*</v>
+      </c>
+    </row>
+    <row r="275" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275" s="6"/>
       <c r="B275" s="6"/>
       <c r="C275" s="33" t="s">
@@ -8831,8 +11949,15 @@
       <c r="J275" s="28">
         <v>165</v>
       </c>
-    </row>
-    <row r="276" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K275" s="42" t="s">
+        <v>700</v>
+      </c>
+      <c r="L275" s="44" t="str">
+        <f t="shared" si="4"/>
+        <v>*P0213*</v>
+      </c>
+    </row>
+    <row r="276" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" s="6"/>
       <c r="B276" s="6"/>
       <c r="C276" s="33" t="s">
@@ -8853,8 +11978,15 @@
       <c r="J276" s="28">
         <v>165</v>
       </c>
-    </row>
-    <row r="277" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K276" s="42" t="s">
+        <v>701</v>
+      </c>
+      <c r="L276" s="44" t="str">
+        <f t="shared" si="4"/>
+        <v>*P0208*</v>
+      </c>
+    </row>
+    <row r="277" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A277" s="6"/>
       <c r="B277" s="6"/>
       <c r="C277" s="33" t="s">
@@ -8875,8 +12007,15 @@
       <c r="J277" s="28">
         <v>165</v>
       </c>
-    </row>
-    <row r="278" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K277" s="42" t="s">
+        <v>702</v>
+      </c>
+      <c r="L277" s="44" t="str">
+        <f t="shared" si="4"/>
+        <v>*P0210*</v>
+      </c>
+    </row>
+    <row r="278" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A278" s="6"/>
       <c r="B278" s="6"/>
       <c r="C278" s="33" t="s">
@@ -8897,8 +12036,15 @@
       <c r="J278" s="28">
         <v>150</v>
       </c>
-    </row>
-    <row r="279" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K278" s="42" t="s">
+        <v>703</v>
+      </c>
+      <c r="L278" s="44" t="str">
+        <f t="shared" si="4"/>
+        <v>*P0105*</v>
+      </c>
+    </row>
+    <row r="279" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279" s="6"/>
       <c r="B279" s="6"/>
       <c r="C279" s="33" t="s">
@@ -8919,8 +12065,15 @@
       <c r="J279" s="28">
         <v>80</v>
       </c>
-    </row>
-    <row r="280" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K279" s="42" t="s">
+        <v>704</v>
+      </c>
+      <c r="L279" s="44" t="str">
+        <f t="shared" si="4"/>
+        <v>*P0222*</v>
+      </c>
+    </row>
+    <row r="280" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" s="6"/>
       <c r="B280" s="6"/>
       <c r="C280" s="33" t="s">
@@ -8941,8 +12094,15 @@
       <c r="J280" s="28">
         <v>80</v>
       </c>
-    </row>
-    <row r="281" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K280" s="42" t="s">
+        <v>705</v>
+      </c>
+      <c r="L280" s="44" t="str">
+        <f t="shared" si="4"/>
+        <v>*P0225*</v>
+      </c>
+    </row>
+    <row r="281" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281" s="6"/>
       <c r="B281" s="6"/>
       <c r="C281" s="33" t="s">
@@ -8963,8 +12123,15 @@
       <c r="J281" s="28">
         <v>80</v>
       </c>
-    </row>
-    <row r="282" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K281" s="42" t="s">
+        <v>706</v>
+      </c>
+      <c r="L281" s="44" t="str">
+        <f t="shared" si="4"/>
+        <v>*P0223*</v>
+      </c>
+    </row>
+    <row r="282" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" s="6"/>
       <c r="B282" s="6"/>
       <c r="C282" s="33" t="s">
@@ -8985,8 +12152,15 @@
       <c r="J282" s="28">
         <v>80</v>
       </c>
-    </row>
-    <row r="283" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K282" s="42" t="s">
+        <v>707</v>
+      </c>
+      <c r="L282" s="44" t="str">
+        <f t="shared" si="4"/>
+        <v>*P0220*</v>
+      </c>
+    </row>
+    <row r="283" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283" s="6"/>
       <c r="B283" s="6"/>
       <c r="C283" s="33" t="s">
@@ -9007,8 +12181,15 @@
       <c r="J283" s="28">
         <v>80</v>
       </c>
-    </row>
-    <row r="284" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K283" s="42" t="s">
+        <v>708</v>
+      </c>
+      <c r="L283" s="44" t="str">
+        <f t="shared" si="4"/>
+        <v>*P0221*</v>
+      </c>
+    </row>
+    <row r="284" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284" s="6"/>
       <c r="B284" s="6"/>
       <c r="C284" s="33" t="s">
@@ -9029,8 +12210,15 @@
       <c r="J284" s="28">
         <v>80</v>
       </c>
-    </row>
-    <row r="285" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K284" s="42" t="s">
+        <v>709</v>
+      </c>
+      <c r="L284" s="44" t="str">
+        <f t="shared" si="4"/>
+        <v>*P0219*</v>
+      </c>
+    </row>
+    <row r="285" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A285" s="6"/>
       <c r="B285" s="6"/>
       <c r="C285" s="33" t="s">
@@ -9051,8 +12239,15 @@
       <c r="J285" s="28">
         <v>80</v>
       </c>
-    </row>
-    <row r="286" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K285" s="42" t="s">
+        <v>710</v>
+      </c>
+      <c r="L285" s="44" t="str">
+        <f t="shared" si="4"/>
+        <v>*P0224*</v>
+      </c>
+    </row>
+    <row r="286" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A286" s="6"/>
       <c r="B286" s="6"/>
       <c r="C286" s="33" t="s">
@@ -9073,8 +12268,15 @@
       <c r="J286" s="28">
         <v>80</v>
       </c>
-    </row>
-    <row r="287" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K286" s="42" t="s">
+        <v>711</v>
+      </c>
+      <c r="L286" s="44" t="str">
+        <f t="shared" si="4"/>
+        <v>*P0203*</v>
+      </c>
+    </row>
+    <row r="287" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287" s="6"/>
       <c r="B287" s="6"/>
       <c r="C287" s="33" t="s">
@@ -9095,8 +12297,15 @@
       <c r="J287" s="28">
         <v>165</v>
       </c>
-    </row>
-    <row r="288" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K287" s="42" t="s">
+        <v>712</v>
+      </c>
+      <c r="L287" s="44" t="str">
+        <f t="shared" si="4"/>
+        <v>*P0205*</v>
+      </c>
+    </row>
+    <row r="288" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288" s="6"/>
       <c r="B288" s="6"/>
       <c r="C288" s="33" t="s">
@@ -9117,8 +12326,15 @@
       <c r="J288" s="28">
         <v>165</v>
       </c>
-    </row>
-    <row r="289" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K288" s="42" t="s">
+        <v>713</v>
+      </c>
+      <c r="L288" s="44" t="str">
+        <f t="shared" si="4"/>
+        <v>*P0206*</v>
+      </c>
+    </row>
+    <row r="289" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A289" s="6"/>
       <c r="B289" s="6"/>
       <c r="C289" s="33" t="s">
@@ -9139,8 +12355,15 @@
       <c r="J289" s="28">
         <v>165</v>
       </c>
-    </row>
-    <row r="290" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K289" s="42" t="s">
+        <v>714</v>
+      </c>
+      <c r="L289" s="44" t="str">
+        <f t="shared" si="4"/>
+        <v>*P0204*</v>
+      </c>
+    </row>
+    <row r="290" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A290" s="6"/>
       <c r="B290" s="6"/>
       <c r="C290" s="33" t="s">
@@ -9165,8 +12388,15 @@
       <c r="J290" s="28">
         <v>70</v>
       </c>
-    </row>
-    <row r="291" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K290" s="42" t="s">
+        <v>715</v>
+      </c>
+      <c r="L290" s="44" t="str">
+        <f t="shared" si="4"/>
+        <v>*P0152*</v>
+      </c>
+    </row>
+    <row r="291" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A291" s="6"/>
       <c r="B291" s="6"/>
       <c r="C291" s="33" t="s">
@@ -9191,8 +12421,15 @@
       <c r="J291" s="28">
         <v>70</v>
       </c>
-    </row>
-    <row r="292" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K291" s="42" t="s">
+        <v>716</v>
+      </c>
+      <c r="L291" s="44" t="str">
+        <f t="shared" si="4"/>
+        <v>*P0150*</v>
+      </c>
+    </row>
+    <row r="292" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A292" s="6"/>
       <c r="B292" s="6"/>
       <c r="C292" s="33" t="s">
@@ -9217,8 +12454,15 @@
       <c r="J292" s="28">
         <v>70</v>
       </c>
-    </row>
-    <row r="293" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K292" s="42" t="s">
+        <v>717</v>
+      </c>
+      <c r="L292" s="44" t="str">
+        <f t="shared" si="4"/>
+        <v>*P0151*</v>
+      </c>
+    </row>
+    <row r="293" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="6"/>
       <c r="B293" s="6"/>
       <c r="C293" s="33" t="s">
@@ -9243,8 +12487,15 @@
       <c r="J293" s="28">
         <v>70</v>
       </c>
-    </row>
-    <row r="294" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K293" s="42" t="s">
+        <v>718</v>
+      </c>
+      <c r="L293" s="44" t="str">
+        <f t="shared" si="4"/>
+        <v>*P0149*</v>
+      </c>
+    </row>
+    <row r="294" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A294" s="6"/>
       <c r="B294" s="6"/>
       <c r="C294" s="33" t="s">
@@ -9269,8 +12520,15 @@
       <c r="J294" s="28">
         <v>70</v>
       </c>
-    </row>
-    <row r="295" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K294" s="42" t="s">
+        <v>719</v>
+      </c>
+      <c r="L294" s="44" t="str">
+        <f t="shared" si="4"/>
+        <v>*P0153*</v>
+      </c>
+    </row>
+    <row r="295" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A295" s="6"/>
       <c r="B295" s="6"/>
       <c r="C295" s="33" t="s">
@@ -9295,8 +12553,15 @@
       <c r="J295" s="28">
         <v>90</v>
       </c>
-    </row>
-    <row r="296" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K295" s="42" t="s">
+        <v>720</v>
+      </c>
+      <c r="L295" s="44" t="str">
+        <f t="shared" si="4"/>
+        <v>*P0226*</v>
+      </c>
+    </row>
+    <row r="296" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" s="6"/>
       <c r="B296" s="6"/>
       <c r="C296" s="33" t="s">
@@ -9321,8 +12586,15 @@
       <c r="J296" s="28">
         <v>90</v>
       </c>
-    </row>
-    <row r="297" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K296" s="42" t="s">
+        <v>721</v>
+      </c>
+      <c r="L296" s="44" t="str">
+        <f t="shared" si="4"/>
+        <v>*P0227*</v>
+      </c>
+    </row>
+    <row r="297" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A297" s="6"/>
       <c r="B297" s="6"/>
       <c r="C297" s="33" t="s">
@@ -9343,8 +12615,15 @@
       <c r="J297" s="28">
         <v>100</v>
       </c>
-    </row>
-    <row r="298" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K297" s="42" t="s">
+        <v>722</v>
+      </c>
+      <c r="L297" s="44" t="str">
+        <f t="shared" si="4"/>
+        <v>*P0228*</v>
+      </c>
+    </row>
+    <row r="298" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A298" s="6"/>
       <c r="B298" s="6"/>
       <c r="C298" s="33" t="s">
@@ -9365,8 +12644,15 @@
       <c r="J298" s="28">
         <v>150</v>
       </c>
-    </row>
-    <row r="299" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K298" s="42" t="s">
+        <v>723</v>
+      </c>
+      <c r="L298" s="44" t="str">
+        <f t="shared" si="4"/>
+        <v>*P0043*</v>
+      </c>
+    </row>
+    <row r="299" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A299" s="6"/>
       <c r="B299" s="6"/>
       <c r="C299" s="33" t="s">
@@ -9387,8 +12673,15 @@
       <c r="J299" s="28">
         <v>30</v>
       </c>
-    </row>
-    <row r="300" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K299" s="42" t="s">
+        <v>724</v>
+      </c>
+      <c r="L299" s="44" t="str">
+        <f t="shared" si="4"/>
+        <v>*P0044*</v>
+      </c>
+    </row>
+    <row r="300" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A300" s="6"/>
       <c r="B300" s="6"/>
       <c r="C300" s="34" t="s">
@@ -9409,8 +12702,15 @@
       <c r="J300" s="28">
         <v>65</v>
       </c>
-    </row>
-    <row r="301" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K300" s="42" t="s">
+        <v>725</v>
+      </c>
+      <c r="L300" s="44" t="str">
+        <f t="shared" si="4"/>
+        <v>*P0229*</v>
+      </c>
+    </row>
+    <row r="301" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A301" s="6"/>
       <c r="B301" s="6"/>
       <c r="C301" s="34" t="s">
@@ -9431,8 +12731,15 @@
       <c r="J301" s="28">
         <v>65</v>
       </c>
-    </row>
-    <row r="302" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K301" s="42" t="s">
+        <v>726</v>
+      </c>
+      <c r="L301" s="44" t="str">
+        <f t="shared" si="4"/>
+        <v>*P0230*</v>
+      </c>
+    </row>
+    <row r="302" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A302" s="6"/>
       <c r="B302" s="6"/>
       <c r="C302" s="34" t="s">
@@ -9453,8 +12760,15 @@
       <c r="J302" s="28">
         <v>65</v>
       </c>
-    </row>
-    <row r="303" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K302" s="42" t="s">
+        <v>727</v>
+      </c>
+      <c r="L302" s="44" t="str">
+        <f t="shared" si="4"/>
+        <v>*P0231*</v>
+      </c>
+    </row>
+    <row r="303" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A303" s="6"/>
       <c r="B303" s="6"/>
       <c r="C303" s="34" t="s">
@@ -9475,8 +12789,15 @@
       <c r="J303" s="28">
         <v>65</v>
       </c>
-    </row>
-    <row r="304" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K303" s="42" t="s">
+        <v>728</v>
+      </c>
+      <c r="L303" s="44" t="str">
+        <f t="shared" si="4"/>
+        <v>*P0232*</v>
+      </c>
+    </row>
+    <row r="304" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A304" s="6"/>
       <c r="B304" s="6"/>
       <c r="C304" s="34" t="s">
@@ -9497,8 +12818,15 @@
       <c r="J304" s="28">
         <v>65</v>
       </c>
-    </row>
-    <row r="305" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K304" s="42" t="s">
+        <v>729</v>
+      </c>
+      <c r="L304" s="44" t="str">
+        <f t="shared" si="4"/>
+        <v>*P0233*</v>
+      </c>
+    </row>
+    <row r="305" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A305" s="6"/>
       <c r="B305" s="6"/>
       <c r="C305" s="34" t="s">
@@ -9519,8 +12847,15 @@
       <c r="J305" s="28">
         <v>65</v>
       </c>
-    </row>
-    <row r="306" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K305" s="42" t="s">
+        <v>730</v>
+      </c>
+      <c r="L305" s="44" t="str">
+        <f t="shared" si="4"/>
+        <v>*P0234*</v>
+      </c>
+    </row>
+    <row r="306" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A306" s="6"/>
       <c r="B306" s="6"/>
       <c r="C306" s="33" t="s">
@@ -9541,8 +12876,15 @@
       <c r="J306" s="28">
         <v>65</v>
       </c>
-    </row>
-    <row r="307" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K306" s="42" t="s">
+        <v>731</v>
+      </c>
+      <c r="L306" s="44" t="str">
+        <f t="shared" si="4"/>
+        <v>*P0235*</v>
+      </c>
+    </row>
+    <row r="307" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A307" s="6"/>
       <c r="B307" s="6"/>
       <c r="C307" s="33" t="s">
@@ -9563,8 +12905,15 @@
       <c r="J307" s="28">
         <v>65</v>
       </c>
-    </row>
-    <row r="308" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K307" s="42" t="s">
+        <v>732</v>
+      </c>
+      <c r="L307" s="44" t="str">
+        <f t="shared" si="4"/>
+        <v>*P0236*</v>
+      </c>
+    </row>
+    <row r="308" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A308" s="6"/>
       <c r="B308" s="6"/>
       <c r="C308" s="33" t="s">
@@ -9585,8 +12934,15 @@
       <c r="J308" s="28">
         <v>65</v>
       </c>
-    </row>
-    <row r="309" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K308" s="42" t="s">
+        <v>733</v>
+      </c>
+      <c r="L308" s="44" t="str">
+        <f t="shared" si="4"/>
+        <v>*P0237*</v>
+      </c>
+    </row>
+    <row r="309" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A309" s="6"/>
       <c r="B309" s="6"/>
       <c r="C309" s="33" t="s">
@@ -9607,8 +12963,15 @@
       <c r="J309" s="28">
         <v>65</v>
       </c>
-    </row>
-    <row r="310" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K309" s="42" t="s">
+        <v>734</v>
+      </c>
+      <c r="L309" s="44" t="str">
+        <f t="shared" si="4"/>
+        <v>*P0238*</v>
+      </c>
+    </row>
+    <row r="310" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A310" s="6"/>
       <c r="B310" s="6"/>
       <c r="C310" s="33" t="s">
@@ -9629,8 +12992,15 @@
       <c r="J310" s="28">
         <v>65</v>
       </c>
-    </row>
-    <row r="311" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K310" s="42" t="s">
+        <v>735</v>
+      </c>
+      <c r="L310" s="44" t="str">
+        <f t="shared" si="4"/>
+        <v>*P0239*</v>
+      </c>
+    </row>
+    <row r="311" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A311" s="6"/>
       <c r="B311" s="6"/>
       <c r="C311" s="33" t="s">
@@ -9651,8 +13021,15 @@
       <c r="J311" s="28">
         <v>65</v>
       </c>
-    </row>
-    <row r="312" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K311" s="42" t="s">
+        <v>736</v>
+      </c>
+      <c r="L311" s="44" t="str">
+        <f t="shared" si="4"/>
+        <v>*P0240*</v>
+      </c>
+    </row>
+    <row r="312" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="6"/>
       <c r="B312" s="6"/>
       <c r="C312" s="33" t="s">
@@ -9673,8 +13050,15 @@
       <c r="J312" s="28">
         <v>65</v>
       </c>
-    </row>
-    <row r="313" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K312" s="42" t="s">
+        <v>737</v>
+      </c>
+      <c r="L312" s="44" t="str">
+        <f t="shared" si="4"/>
+        <v>*P0241*</v>
+      </c>
+    </row>
+    <row r="313" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A313" s="6"/>
       <c r="B313" s="6"/>
       <c r="C313" s="33" t="s">
@@ -9695,8 +13079,15 @@
       <c r="J313" s="28">
         <v>65</v>
       </c>
-    </row>
-    <row r="314" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K313" s="42" t="s">
+        <v>738</v>
+      </c>
+      <c r="L313" s="44" t="str">
+        <f t="shared" si="4"/>
+        <v>*P0242*</v>
+      </c>
+    </row>
+    <row r="314" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A314" s="6"/>
       <c r="B314" s="6"/>
       <c r="C314" s="33" t="s">
@@ -9717,8 +13108,15 @@
       <c r="J314" s="28">
         <v>65</v>
       </c>
-    </row>
-    <row r="315" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K314" s="42" t="s">
+        <v>739</v>
+      </c>
+      <c r="L314" s="44" t="str">
+        <f t="shared" si="4"/>
+        <v>*P0243*</v>
+      </c>
+    </row>
+    <row r="315" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A315" s="6"/>
       <c r="B315" s="6"/>
       <c r="C315" s="33" t="s">
@@ -9739,8 +13137,15 @@
       <c r="J315" s="28">
         <v>65</v>
       </c>
-    </row>
-    <row r="316" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K315" s="42" t="s">
+        <v>740</v>
+      </c>
+      <c r="L315" s="44" t="str">
+        <f t="shared" si="4"/>
+        <v>*P0244*</v>
+      </c>
+    </row>
+    <row r="316" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A316" s="6"/>
       <c r="B316" s="6"/>
       <c r="C316" s="33" t="s">
@@ -9761,8 +13166,15 @@
       <c r="J316" s="28">
         <v>65</v>
       </c>
-    </row>
-    <row r="317" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K316" s="42" t="s">
+        <v>741</v>
+      </c>
+      <c r="L316" s="44" t="str">
+        <f t="shared" si="4"/>
+        <v>*P0245*</v>
+      </c>
+    </row>
+    <row r="317" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A317" s="6"/>
       <c r="B317" s="6"/>
       <c r="C317" s="33" t="s">
@@ -9783,8 +13195,15 @@
       <c r="J317" s="28">
         <v>65</v>
       </c>
-    </row>
-    <row r="318" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K317" s="42" t="s">
+        <v>742</v>
+      </c>
+      <c r="L317" s="44" t="str">
+        <f t="shared" si="4"/>
+        <v>*P0246*</v>
+      </c>
+    </row>
+    <row r="318" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A318" s="6"/>
       <c r="B318" s="6"/>
       <c r="C318" s="33" t="s">
@@ -9805,8 +13224,15 @@
       <c r="J318" s="28">
         <v>65</v>
       </c>
-    </row>
-    <row r="319" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K318" s="42" t="s">
+        <v>743</v>
+      </c>
+      <c r="L318" s="44" t="str">
+        <f t="shared" si="4"/>
+        <v>*P0247*</v>
+      </c>
+    </row>
+    <row r="319" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A319" s="6"/>
       <c r="B319" s="6"/>
       <c r="C319" s="33" t="s">
@@ -9827,8 +13253,15 @@
       <c r="J319" s="28">
         <v>65</v>
       </c>
-    </row>
-    <row r="320" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K319" s="42" t="s">
+        <v>744</v>
+      </c>
+      <c r="L319" s="44" t="str">
+        <f t="shared" si="4"/>
+        <v>*P0248*</v>
+      </c>
+    </row>
+    <row r="320" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A320" s="6"/>
       <c r="B320" s="6"/>
       <c r="C320" s="33" t="s">
@@ -9849,8 +13282,15 @@
       <c r="J320" s="28">
         <v>65</v>
       </c>
-    </row>
-    <row r="321" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K320" s="42" t="s">
+        <v>745</v>
+      </c>
+      <c r="L320" s="44" t="str">
+        <f t="shared" si="4"/>
+        <v>*P0249*</v>
+      </c>
+    </row>
+    <row r="321" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A321" s="6"/>
       <c r="B321" s="6"/>
       <c r="C321" s="33" t="s">
@@ -9871,8 +13311,15 @@
       <c r="J321" s="28">
         <v>65</v>
       </c>
-    </row>
-    <row r="322" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K321" s="42" t="s">
+        <v>746</v>
+      </c>
+      <c r="L321" s="44" t="str">
+        <f t="shared" si="4"/>
+        <v>*P0250*</v>
+      </c>
+    </row>
+    <row r="322" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A322" s="6"/>
       <c r="B322" s="6"/>
       <c r="C322" s="33" t="s">
@@ -9893,8 +13340,15 @@
       <c r="J322" s="28">
         <v>65</v>
       </c>
-    </row>
-    <row r="323" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K322" s="42" t="s">
+        <v>747</v>
+      </c>
+      <c r="L322" s="44" t="str">
+        <f t="shared" ref="L322:L385" si="5">"*"&amp;UPPER(K322)&amp;"*"</f>
+        <v>*P0251*</v>
+      </c>
+    </row>
+    <row r="323" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A323" s="6"/>
       <c r="B323" s="6"/>
       <c r="C323" s="33" t="s">
@@ -9915,8 +13369,15 @@
       <c r="J323" s="28">
         <v>65</v>
       </c>
-    </row>
-    <row r="324" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K323" s="42" t="s">
+        <v>748</v>
+      </c>
+      <c r="L323" s="44" t="str">
+        <f t="shared" si="5"/>
+        <v>*P0252*</v>
+      </c>
+    </row>
+    <row r="324" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A324" s="6"/>
       <c r="B324" s="6"/>
       <c r="C324" s="35" t="s">
@@ -9937,8 +13398,15 @@
       <c r="J324" s="28">
         <v>90</v>
       </c>
-    </row>
-    <row r="325" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K324" s="42" t="s">
+        <v>749</v>
+      </c>
+      <c r="L324" s="44" t="str">
+        <f t="shared" si="5"/>
+        <v>*P0265*</v>
+      </c>
+    </row>
+    <row r="325" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A325" s="6"/>
       <c r="B325" s="6"/>
       <c r="C325" s="35" t="s">
@@ -9959,8 +13427,15 @@
       <c r="J325" s="28">
         <v>90</v>
       </c>
-    </row>
-    <row r="326" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K325" s="42" t="s">
+        <v>750</v>
+      </c>
+      <c r="L325" s="44" t="str">
+        <f t="shared" si="5"/>
+        <v>*P0266*</v>
+      </c>
+    </row>
+    <row r="326" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A326" s="6"/>
       <c r="B326" s="6"/>
       <c r="C326" s="35" t="s">
@@ -9981,8 +13456,15 @@
       <c r="J326" s="28">
         <v>90</v>
       </c>
-    </row>
-    <row r="327" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K326" s="42" t="s">
+        <v>751</v>
+      </c>
+      <c r="L326" s="44" t="str">
+        <f t="shared" si="5"/>
+        <v>*P0267*</v>
+      </c>
+    </row>
+    <row r="327" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A327" s="6"/>
       <c r="B327" s="6"/>
       <c r="C327" s="35" t="s">
@@ -10003,8 +13485,15 @@
       <c r="J327" s="28">
         <v>90</v>
       </c>
-    </row>
-    <row r="328" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K327" s="42" t="s">
+        <v>752</v>
+      </c>
+      <c r="L327" s="44" t="str">
+        <f t="shared" si="5"/>
+        <v>*P0268*</v>
+      </c>
+    </row>
+    <row r="328" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A328" s="6"/>
       <c r="B328" s="6"/>
       <c r="C328" s="35" t="s">
@@ -10025,8 +13514,15 @@
       <c r="J328" s="28">
         <v>90</v>
       </c>
-    </row>
-    <row r="329" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K328" s="42" t="s">
+        <v>753</v>
+      </c>
+      <c r="L328" s="44" t="str">
+        <f t="shared" si="5"/>
+        <v>*P0269*</v>
+      </c>
+    </row>
+    <row r="329" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A329" s="6"/>
       <c r="B329" s="6"/>
       <c r="C329" s="35" t="s">
@@ -10047,8 +13543,15 @@
       <c r="J329" s="28">
         <v>90</v>
       </c>
-    </row>
-    <row r="330" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K329" s="42" t="s">
+        <v>754</v>
+      </c>
+      <c r="L329" s="44" t="str">
+        <f t="shared" si="5"/>
+        <v>*P0270*</v>
+      </c>
+    </row>
+    <row r="330" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A330" s="6"/>
       <c r="B330" s="6"/>
       <c r="C330" s="35" t="s">
@@ -10069,8 +13572,15 @@
       <c r="J330" s="28">
         <v>90</v>
       </c>
-    </row>
-    <row r="331" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K330" s="42" t="s">
+        <v>755</v>
+      </c>
+      <c r="L330" s="44" t="str">
+        <f t="shared" si="5"/>
+        <v>*P0271*</v>
+      </c>
+    </row>
+    <row r="331" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A331" s="6"/>
       <c r="B331" s="6"/>
       <c r="C331" s="33" t="s">
@@ -10091,8 +13601,15 @@
       <c r="J331" s="28">
         <v>90</v>
       </c>
-    </row>
-    <row r="332" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K331" s="42" t="s">
+        <v>756</v>
+      </c>
+      <c r="L331" s="44" t="str">
+        <f t="shared" si="5"/>
+        <v>*P0272*</v>
+      </c>
+    </row>
+    <row r="332" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A332" s="6"/>
       <c r="B332" s="6"/>
       <c r="C332" s="33" t="s">
@@ -10113,8 +13630,15 @@
       <c r="J332" s="28">
         <v>90</v>
       </c>
-    </row>
-    <row r="333" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K332" s="42" t="s">
+        <v>757</v>
+      </c>
+      <c r="L332" s="44" t="str">
+        <f t="shared" si="5"/>
+        <v>*P0273*</v>
+      </c>
+    </row>
+    <row r="333" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A333" s="6"/>
       <c r="B333" s="6"/>
       <c r="C333" s="33" t="s">
@@ -10135,8 +13659,15 @@
       <c r="J333" s="28">
         <v>90</v>
       </c>
-    </row>
-    <row r="334" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K333" s="42" t="s">
+        <v>758</v>
+      </c>
+      <c r="L333" s="44" t="str">
+        <f t="shared" si="5"/>
+        <v>*P0274*</v>
+      </c>
+    </row>
+    <row r="334" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A334" s="6"/>
       <c r="B334" s="6"/>
       <c r="C334" s="33" t="s">
@@ -10157,8 +13688,15 @@
       <c r="J334" s="28">
         <v>90</v>
       </c>
-    </row>
-    <row r="335" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K334" s="42" t="s">
+        <v>759</v>
+      </c>
+      <c r="L334" s="44" t="str">
+        <f t="shared" si="5"/>
+        <v>*P0275*</v>
+      </c>
+    </row>
+    <row r="335" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A335" s="6"/>
       <c r="B335" s="6"/>
       <c r="C335" s="33" t="s">
@@ -10179,8 +13717,15 @@
       <c r="J335" s="28">
         <v>90</v>
       </c>
-    </row>
-    <row r="336" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K335" s="42" t="s">
+        <v>760</v>
+      </c>
+      <c r="L335" s="44" t="str">
+        <f t="shared" si="5"/>
+        <v>*P0138*</v>
+      </c>
+    </row>
+    <row r="336" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A336" s="6"/>
       <c r="B336" s="6"/>
       <c r="C336" s="35" t="s">
@@ -10201,8 +13746,15 @@
       <c r="J336" s="28">
         <v>90</v>
       </c>
-    </row>
-    <row r="337" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K336" s="42" t="s">
+        <v>761</v>
+      </c>
+      <c r="L336" s="44" t="str">
+        <f t="shared" si="5"/>
+        <v>*P0253*</v>
+      </c>
+    </row>
+    <row r="337" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A337" s="6"/>
       <c r="B337" s="6"/>
       <c r="C337" s="35" t="s">
@@ -10223,8 +13775,15 @@
       <c r="J337" s="28">
         <v>90</v>
       </c>
-    </row>
-    <row r="338" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K337" s="42" t="s">
+        <v>762</v>
+      </c>
+      <c r="L337" s="44" t="str">
+        <f t="shared" si="5"/>
+        <v>*P0254*</v>
+      </c>
+    </row>
+    <row r="338" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A338" s="6"/>
       <c r="B338" s="6"/>
       <c r="C338" s="35" t="s">
@@ -10245,8 +13804,15 @@
       <c r="J338" s="28">
         <v>90</v>
       </c>
-    </row>
-    <row r="339" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K338" s="42" t="s">
+        <v>763</v>
+      </c>
+      <c r="L338" s="44" t="str">
+        <f t="shared" si="5"/>
+        <v>*P0255*</v>
+      </c>
+    </row>
+    <row r="339" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A339" s="6"/>
       <c r="B339" s="6"/>
       <c r="C339" s="35" t="s">
@@ -10267,8 +13833,15 @@
       <c r="J339" s="28">
         <v>90</v>
       </c>
-    </row>
-    <row r="340" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K339" s="42" t="s">
+        <v>764</v>
+      </c>
+      <c r="L339" s="44" t="str">
+        <f t="shared" si="5"/>
+        <v>*P0256*</v>
+      </c>
+    </row>
+    <row r="340" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A340" s="6"/>
       <c r="B340" s="6"/>
       <c r="C340" s="35" t="s">
@@ -10289,8 +13862,15 @@
       <c r="J340" s="28">
         <v>90</v>
       </c>
-    </row>
-    <row r="341" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K340" s="42" t="s">
+        <v>765</v>
+      </c>
+      <c r="L340" s="44" t="str">
+        <f t="shared" si="5"/>
+        <v>*P0257*</v>
+      </c>
+    </row>
+    <row r="341" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A341" s="6"/>
       <c r="B341" s="6"/>
       <c r="C341" s="35" t="s">
@@ -10311,8 +13891,15 @@
       <c r="J341" s="28">
         <v>90</v>
       </c>
-    </row>
-    <row r="342" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K341" s="42" t="s">
+        <v>766</v>
+      </c>
+      <c r="L341" s="44" t="str">
+        <f t="shared" si="5"/>
+        <v>*P0258*</v>
+      </c>
+    </row>
+    <row r="342" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A342" s="6"/>
       <c r="B342" s="6"/>
       <c r="C342" s="35" t="s">
@@ -10333,8 +13920,15 @@
       <c r="J342" s="28">
         <v>90</v>
       </c>
-    </row>
-    <row r="343" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K342" s="42" t="s">
+        <v>767</v>
+      </c>
+      <c r="L342" s="44" t="str">
+        <f t="shared" si="5"/>
+        <v>*P0259*</v>
+      </c>
+    </row>
+    <row r="343" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A343" s="6"/>
       <c r="B343" s="6"/>
       <c r="C343" s="35" t="s">
@@ -10355,8 +13949,15 @@
       <c r="J343" s="28">
         <v>90</v>
       </c>
-    </row>
-    <row r="344" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K343" s="42" t="s">
+        <v>768</v>
+      </c>
+      <c r="L343" s="44" t="str">
+        <f t="shared" si="5"/>
+        <v>*P0260*</v>
+      </c>
+    </row>
+    <row r="344" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A344" s="6"/>
       <c r="B344" s="6"/>
       <c r="C344" s="35" t="s">
@@ -10377,8 +13978,15 @@
       <c r="J344" s="28">
         <v>90</v>
       </c>
-    </row>
-    <row r="345" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K344" s="42" t="s">
+        <v>769</v>
+      </c>
+      <c r="L344" s="44" t="str">
+        <f t="shared" si="5"/>
+        <v>*P0261*</v>
+      </c>
+    </row>
+    <row r="345" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A345" s="6"/>
       <c r="B345" s="6"/>
       <c r="C345" s="35" t="s">
@@ -10399,8 +14007,15 @@
       <c r="J345" s="28">
         <v>90</v>
       </c>
-    </row>
-    <row r="346" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K345" s="42" t="s">
+        <v>770</v>
+      </c>
+      <c r="L345" s="44" t="str">
+        <f t="shared" si="5"/>
+        <v>*P0264*</v>
+      </c>
+    </row>
+    <row r="346" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A346" s="6"/>
       <c r="B346" s="6"/>
       <c r="C346" s="35" t="s">
@@ -10421,8 +14036,15 @@
       <c r="J346" s="28">
         <v>90</v>
       </c>
-    </row>
-    <row r="347" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K346" s="42" t="s">
+        <v>771</v>
+      </c>
+      <c r="L346" s="44" t="str">
+        <f t="shared" si="5"/>
+        <v>*P0262*</v>
+      </c>
+    </row>
+    <row r="347" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A347" s="6"/>
       <c r="B347" s="6"/>
       <c r="C347" s="35" t="s">
@@ -10443,8 +14065,15 @@
       <c r="J347" s="28">
         <v>90</v>
       </c>
-    </row>
-    <row r="348" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K347" s="42" t="s">
+        <v>772</v>
+      </c>
+      <c r="L347" s="44" t="str">
+        <f t="shared" si="5"/>
+        <v>*P0263*</v>
+      </c>
+    </row>
+    <row r="348" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A348" s="6"/>
       <c r="B348" s="6"/>
       <c r="C348" s="33" t="s">
@@ -10465,8 +14094,15 @@
       <c r="J348" s="28">
         <v>65</v>
       </c>
-    </row>
-    <row r="349" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K348" s="42" t="s">
+        <v>773</v>
+      </c>
+      <c r="L348" s="44" t="str">
+        <f t="shared" si="5"/>
+        <v>*P0217*</v>
+      </c>
+    </row>
+    <row r="349" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A349" s="6"/>
       <c r="B349" s="6"/>
       <c r="C349" s="33" t="s">
@@ -10487,8 +14123,15 @@
       <c r="J349" s="28">
         <v>65</v>
       </c>
-    </row>
-    <row r="350" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K349" s="42" t="s">
+        <v>774</v>
+      </c>
+      <c r="L349" s="44" t="str">
+        <f t="shared" si="5"/>
+        <v>*P0216*</v>
+      </c>
+    </row>
+    <row r="350" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A350" s="6"/>
       <c r="B350" s="6"/>
       <c r="C350" s="33" t="s">
@@ -10509,8 +14152,15 @@
       <c r="J350" s="28">
         <v>65</v>
       </c>
-    </row>
-    <row r="351" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K350" s="42" t="s">
+        <v>775</v>
+      </c>
+      <c r="L350" s="44" t="str">
+        <f t="shared" si="5"/>
+        <v>*P0215*</v>
+      </c>
+    </row>
+    <row r="351" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A351" s="6"/>
       <c r="B351" s="6"/>
       <c r="C351" s="33" t="s">
@@ -10531,8 +14181,15 @@
       <c r="J351" s="28">
         <v>65</v>
       </c>
-    </row>
-    <row r="352" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K351" s="42" t="s">
+        <v>776</v>
+      </c>
+      <c r="L351" s="44" t="str">
+        <f t="shared" si="5"/>
+        <v>*P0218*</v>
+      </c>
+    </row>
+    <row r="352" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A352" s="6"/>
       <c r="B352" s="6"/>
       <c r="C352" s="36" t="s">
@@ -10551,8 +14208,15 @@
       <c r="H352" s="28"/>
       <c r="I352" s="28"/>
       <c r="J352" s="28"/>
-    </row>
-    <row r="353" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K352" s="42" t="s">
+        <v>777</v>
+      </c>
+      <c r="L352" s="44" t="str">
+        <f t="shared" si="5"/>
+        <v>*P0316*</v>
+      </c>
+    </row>
+    <row r="353" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A353" s="6"/>
       <c r="B353" s="6"/>
       <c r="C353" s="37" t="s">
@@ -10571,8 +14235,15 @@
       <c r="H353" s="28"/>
       <c r="I353" s="28"/>
       <c r="J353" s="28"/>
-    </row>
-    <row r="354" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K353" s="42" t="s">
+        <v>778</v>
+      </c>
+      <c r="L353" s="44" t="str">
+        <f t="shared" si="5"/>
+        <v>*P0381*</v>
+      </c>
+    </row>
+    <row r="354" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A354" s="6"/>
       <c r="B354" s="6"/>
       <c r="C354" s="36" t="s">
@@ -10591,8 +14262,15 @@
       <c r="H354" s="28"/>
       <c r="I354" s="28"/>
       <c r="J354" s="28"/>
-    </row>
-    <row r="355" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K354" s="42" t="s">
+        <v>779</v>
+      </c>
+      <c r="L354" s="44" t="str">
+        <f t="shared" si="5"/>
+        <v>*P0391*</v>
+      </c>
+    </row>
+    <row r="355" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A355" s="6"/>
       <c r="B355" s="6"/>
       <c r="C355" s="37" t="s">
@@ -10611,8 +14289,15 @@
       <c r="H355" s="28"/>
       <c r="I355" s="28"/>
       <c r="J355" s="28"/>
-    </row>
-    <row r="356" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K355" s="42" t="s">
+        <v>780</v>
+      </c>
+      <c r="L355" s="44" t="str">
+        <f t="shared" si="5"/>
+        <v>*P0382*</v>
+      </c>
+    </row>
+    <row r="356" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A356" s="6"/>
       <c r="B356" s="6"/>
       <c r="C356" s="36" t="s">
@@ -10631,8 +14316,15 @@
       <c r="H356" s="28"/>
       <c r="I356" s="28"/>
       <c r="J356" s="28"/>
-    </row>
-    <row r="357" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K356" s="42" t="s">
+        <v>781</v>
+      </c>
+      <c r="L356" s="44" t="str">
+        <f t="shared" si="5"/>
+        <v>*P0317*</v>
+      </c>
+    </row>
+    <row r="357" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A357" s="6"/>
       <c r="B357" s="6"/>
       <c r="C357" s="37" t="s">
@@ -10651,8 +14343,15 @@
       <c r="H357" s="28"/>
       <c r="I357" s="28"/>
       <c r="J357" s="28"/>
-    </row>
-    <row r="358" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K357" s="42" t="s">
+        <v>782</v>
+      </c>
+      <c r="L357" s="44" t="str">
+        <f t="shared" si="5"/>
+        <v>*P0392*</v>
+      </c>
+    </row>
+    <row r="358" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A358" s="6"/>
       <c r="B358" s="6"/>
       <c r="C358" s="36" t="s">
@@ -10671,8 +14370,15 @@
       <c r="H358" s="28"/>
       <c r="I358" s="28"/>
       <c r="J358" s="28"/>
-    </row>
-    <row r="359" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K358" s="42" t="s">
+        <v>783</v>
+      </c>
+      <c r="L358" s="44" t="str">
+        <f t="shared" si="5"/>
+        <v>*P0318*</v>
+      </c>
+    </row>
+    <row r="359" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A359" s="6"/>
       <c r="B359" s="6"/>
       <c r="C359" s="37" t="s">
@@ -10691,8 +14397,15 @@
       <c r="H359" s="28"/>
       <c r="I359" s="28"/>
       <c r="J359" s="28"/>
-    </row>
-    <row r="360" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K359" s="42" t="s">
+        <v>784</v>
+      </c>
+      <c r="L359" s="44" t="str">
+        <f t="shared" si="5"/>
+        <v>*P0383*</v>
+      </c>
+    </row>
+    <row r="360" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A360" s="6"/>
       <c r="B360" s="6"/>
       <c r="C360" s="37" t="s">
@@ -10711,8 +14424,15 @@
       <c r="H360" s="28"/>
       <c r="I360" s="28"/>
       <c r="J360" s="28"/>
-    </row>
-    <row r="361" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K360" s="42" t="s">
+        <v>785</v>
+      </c>
+      <c r="L360" s="44" t="str">
+        <f t="shared" si="5"/>
+        <v>*P0016*</v>
+      </c>
+    </row>
+    <row r="361" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A361" s="6"/>
       <c r="B361" s="6"/>
       <c r="C361" s="37" t="s">
@@ -10731,8 +14451,15 @@
       <c r="H361" s="28"/>
       <c r="I361" s="28"/>
       <c r="J361" s="28"/>
-    </row>
-    <row r="362" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K361" s="42" t="s">
+        <v>786</v>
+      </c>
+      <c r="L361" s="44" t="str">
+        <f t="shared" si="5"/>
+        <v>*P0102*</v>
+      </c>
+    </row>
+    <row r="362" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A362" s="6"/>
       <c r="B362" s="6"/>
       <c r="C362" s="37" t="s">
@@ -10751,8 +14478,15 @@
       <c r="H362" s="28"/>
       <c r="I362" s="28"/>
       <c r="J362" s="28"/>
-    </row>
-    <row r="363" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K362" s="42" t="s">
+        <v>787</v>
+      </c>
+      <c r="L362" s="44" t="str">
+        <f t="shared" si="5"/>
+        <v>*P0319*</v>
+      </c>
+    </row>
+    <row r="363" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A363" s="6"/>
       <c r="B363" s="6"/>
       <c r="C363" s="37" t="s">
@@ -10771,8 +14505,15 @@
       <c r="H363" s="28"/>
       <c r="I363" s="28"/>
       <c r="J363" s="28"/>
-    </row>
-    <row r="364" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K363" s="42" t="s">
+        <v>788</v>
+      </c>
+      <c r="L363" s="44" t="str">
+        <f t="shared" si="5"/>
+        <v>*P0384*</v>
+      </c>
+    </row>
+    <row r="364" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A364" s="6"/>
       <c r="B364" s="6"/>
       <c r="C364" s="38" t="s">
@@ -10797,8 +14538,15 @@
       <c r="J364" s="28">
         <v>250</v>
       </c>
-    </row>
-    <row r="365" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K364" s="42" t="s">
+        <v>789</v>
+      </c>
+      <c r="L364" s="44" t="str">
+        <f t="shared" si="5"/>
+        <v>*P0047*</v>
+      </c>
+    </row>
+    <row r="365" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A365" s="6"/>
       <c r="B365" s="6"/>
       <c r="C365" s="39" t="s">
@@ -10823,8 +14571,15 @@
       <c r="J365" s="28">
         <v>250</v>
       </c>
-    </row>
-    <row r="366" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K365" s="42" t="s">
+        <v>790</v>
+      </c>
+      <c r="L365" s="44" t="str">
+        <f t="shared" si="5"/>
+        <v>*P0048*</v>
+      </c>
+    </row>
+    <row r="366" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A366" s="6"/>
       <c r="B366" s="6"/>
       <c r="C366" s="38" t="s">
@@ -10849,8 +14604,15 @@
       <c r="J366" s="28">
         <v>250</v>
       </c>
-    </row>
-    <row r="367" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K366" s="42" t="s">
+        <v>791</v>
+      </c>
+      <c r="L366" s="44" t="str">
+        <f t="shared" si="5"/>
+        <v>*P0049*</v>
+      </c>
+    </row>
+    <row r="367" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A367" s="6"/>
       <c r="B367" s="6"/>
       <c r="C367" s="38" t="s">
@@ -10875,8 +14637,15 @@
       <c r="J367" s="28">
         <v>250</v>
       </c>
-    </row>
-    <row r="368" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K367" s="42" t="s">
+        <v>792</v>
+      </c>
+      <c r="L367" s="44" t="str">
+        <f t="shared" si="5"/>
+        <v>*P0050*</v>
+      </c>
+    </row>
+    <row r="368" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A368" s="6"/>
       <c r="B368" s="6"/>
       <c r="C368" s="38" t="s">
@@ -10901,8 +14670,15 @@
       <c r="J368" s="28">
         <v>250</v>
       </c>
-    </row>
-    <row r="369" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K368" s="42" t="s">
+        <v>793</v>
+      </c>
+      <c r="L368" s="44" t="str">
+        <f t="shared" si="5"/>
+        <v>*P0051*</v>
+      </c>
+    </row>
+    <row r="369" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A369" s="6"/>
       <c r="B369" s="6"/>
       <c r="C369" s="38" t="s">
@@ -10927,8 +14703,15 @@
       <c r="J369" s="28">
         <v>250</v>
       </c>
-    </row>
-    <row r="370" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K369" s="42" t="s">
+        <v>794</v>
+      </c>
+      <c r="L369" s="44" t="str">
+        <f t="shared" si="5"/>
+        <v>*P0052*</v>
+      </c>
+    </row>
+    <row r="370" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A370" s="6"/>
       <c r="B370" s="6"/>
       <c r="C370" s="38" t="s">
@@ -10953,8 +14736,15 @@
       <c r="J370" s="28">
         <v>250</v>
       </c>
-    </row>
-    <row r="371" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K370" s="42" t="s">
+        <v>795</v>
+      </c>
+      <c r="L370" s="44" t="str">
+        <f t="shared" si="5"/>
+        <v>*P0053*</v>
+      </c>
+    </row>
+    <row r="371" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A371" s="6"/>
       <c r="B371" s="6"/>
       <c r="C371" s="38" t="s">
@@ -10979,8 +14769,15 @@
       <c r="J371" s="28">
         <v>250</v>
       </c>
-    </row>
-    <row r="372" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K371" s="42" t="s">
+        <v>796</v>
+      </c>
+      <c r="L371" s="44" t="str">
+        <f t="shared" si="5"/>
+        <v>*P0054*</v>
+      </c>
+    </row>
+    <row r="372" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A372" s="6"/>
       <c r="B372" s="6"/>
       <c r="C372" s="38" t="s">
@@ -11005,8 +14802,15 @@
       <c r="J372" s="28">
         <v>250</v>
       </c>
-    </row>
-    <row r="373" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K372" s="42" t="s">
+        <v>797</v>
+      </c>
+      <c r="L372" s="44" t="str">
+        <f t="shared" si="5"/>
+        <v>*P0055*</v>
+      </c>
+    </row>
+    <row r="373" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A373" s="6"/>
       <c r="B373" s="6"/>
       <c r="C373" s="38" t="s">
@@ -11031,8 +14835,15 @@
       <c r="J373" s="28">
         <v>250</v>
       </c>
-    </row>
-    <row r="374" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K373" s="42" t="s">
+        <v>798</v>
+      </c>
+      <c r="L373" s="44" t="str">
+        <f t="shared" si="5"/>
+        <v>*P0057*</v>
+      </c>
+    </row>
+    <row r="374" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A374" s="6"/>
       <c r="B374" s="6"/>
       <c r="C374" s="38" t="s">
@@ -11057,8 +14868,15 @@
       <c r="J374" s="28">
         <v>250</v>
       </c>
-    </row>
-    <row r="375" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K374" s="42" t="s">
+        <v>799</v>
+      </c>
+      <c r="L374" s="44" t="str">
+        <f t="shared" si="5"/>
+        <v>*P0056*</v>
+      </c>
+    </row>
+    <row r="375" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A375" s="6"/>
       <c r="B375" s="6"/>
       <c r="C375" s="38" t="s">
@@ -11083,8 +14901,15 @@
       <c r="J375" s="28">
         <v>250</v>
       </c>
-    </row>
-    <row r="376" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K375" s="42" t="s">
+        <v>800</v>
+      </c>
+      <c r="L375" s="44" t="str">
+        <f t="shared" si="5"/>
+        <v>*P0058*</v>
+      </c>
+    </row>
+    <row r="376" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A376" s="6"/>
       <c r="B376" s="6"/>
       <c r="C376" s="38" t="s">
@@ -11109,8 +14934,15 @@
       <c r="J376" s="28">
         <v>250</v>
       </c>
-    </row>
-    <row r="377" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K376" s="42" t="s">
+        <v>801</v>
+      </c>
+      <c r="L376" s="44" t="str">
+        <f t="shared" si="5"/>
+        <v>*P0059*</v>
+      </c>
+    </row>
+    <row r="377" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A377" s="6"/>
       <c r="B377" s="6"/>
       <c r="C377" s="38" t="s">
@@ -11135,8 +14967,15 @@
       <c r="J377" s="28">
         <v>250</v>
       </c>
-    </row>
-    <row r="378" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K377" s="42" t="s">
+        <v>802</v>
+      </c>
+      <c r="L377" s="44" t="str">
+        <f t="shared" si="5"/>
+        <v>*P0061*</v>
+      </c>
+    </row>
+    <row r="378" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A378" s="6"/>
       <c r="B378" s="6"/>
       <c r="C378" s="38" t="s">
@@ -11161,8 +15000,15 @@
       <c r="J378" s="28">
         <v>250</v>
       </c>
-    </row>
-    <row r="379" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K378" s="42" t="s">
+        <v>803</v>
+      </c>
+      <c r="L378" s="44" t="str">
+        <f t="shared" si="5"/>
+        <v>*P0062*</v>
+      </c>
+    </row>
+    <row r="379" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A379" s="6"/>
       <c r="B379" s="6"/>
       <c r="C379" s="38" t="s">
@@ -11187,8 +15033,15 @@
       <c r="J379" s="28">
         <v>250</v>
       </c>
-    </row>
-    <row r="380" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K379" s="42" t="s">
+        <v>804</v>
+      </c>
+      <c r="L379" s="44" t="str">
+        <f t="shared" si="5"/>
+        <v>*P0060*</v>
+      </c>
+    </row>
+    <row r="380" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A380" s="6"/>
       <c r="B380" s="6"/>
       <c r="C380" s="38" t="s">
@@ -11213,8 +15066,15 @@
       <c r="J380" s="28">
         <v>250</v>
       </c>
-    </row>
-    <row r="381" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K380" s="42" t="s">
+        <v>805</v>
+      </c>
+      <c r="L380" s="44" t="str">
+        <f t="shared" si="5"/>
+        <v>*P0066*</v>
+      </c>
+    </row>
+    <row r="381" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A381" s="6"/>
       <c r="B381" s="6"/>
       <c r="C381" s="38" t="s">
@@ -11239,8 +15099,15 @@
       <c r="J381" s="28">
         <v>250</v>
       </c>
-    </row>
-    <row r="382" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K381" s="42" t="s">
+        <v>806</v>
+      </c>
+      <c r="L381" s="44" t="str">
+        <f t="shared" si="5"/>
+        <v>*P0064*</v>
+      </c>
+    </row>
+    <row r="382" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A382" s="6"/>
       <c r="B382" s="6"/>
       <c r="C382" s="38" t="s">
@@ -11265,8 +15132,15 @@
       <c r="J382" s="28">
         <v>250</v>
       </c>
-    </row>
-    <row r="383" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K382" s="42" t="s">
+        <v>807</v>
+      </c>
+      <c r="L382" s="44" t="str">
+        <f t="shared" si="5"/>
+        <v>*P0065*</v>
+      </c>
+    </row>
+    <row r="383" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A383" s="6"/>
       <c r="B383" s="6"/>
       <c r="C383" s="38" t="s">
@@ -11291,8 +15165,15 @@
       <c r="J383" s="28">
         <v>250</v>
       </c>
-    </row>
-    <row r="384" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K383" s="42" t="s">
+        <v>808</v>
+      </c>
+      <c r="L383" s="44" t="str">
+        <f t="shared" si="5"/>
+        <v>*P0063*</v>
+      </c>
+    </row>
+    <row r="384" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A384" s="6"/>
       <c r="B384" s="6"/>
       <c r="C384" s="38" t="s">
@@ -11317,8 +15198,15 @@
       <c r="J384" s="28">
         <v>250</v>
       </c>
-    </row>
-    <row r="385" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K384" s="42" t="s">
+        <v>809</v>
+      </c>
+      <c r="L384" s="44" t="str">
+        <f t="shared" si="5"/>
+        <v>*P0075*</v>
+      </c>
+    </row>
+    <row r="385" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A385" s="6"/>
       <c r="B385" s="6"/>
       <c r="C385" s="38" t="s">
@@ -11343,8 +15231,15 @@
       <c r="J385" s="28">
         <v>250</v>
       </c>
-    </row>
-    <row r="386" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K385" s="42" t="s">
+        <v>810</v>
+      </c>
+      <c r="L385" s="44" t="str">
+        <f t="shared" si="5"/>
+        <v>*P0069*</v>
+      </c>
+    </row>
+    <row r="386" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A386" s="6"/>
       <c r="B386" s="6"/>
       <c r="C386" s="38" t="s">
@@ -11369,8 +15264,15 @@
       <c r="J386" s="28">
         <v>250</v>
       </c>
-    </row>
-    <row r="387" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K386" s="42" t="s">
+        <v>811</v>
+      </c>
+      <c r="L386" s="44" t="str">
+        <f t="shared" ref="L386:L449" si="6">"*"&amp;UPPER(K386)&amp;"*"</f>
+        <v>*P0073*</v>
+      </c>
+    </row>
+    <row r="387" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A387" s="6"/>
       <c r="B387" s="6"/>
       <c r="C387" s="38" t="s">
@@ -11395,8 +15297,15 @@
       <c r="J387" s="28">
         <v>250</v>
       </c>
-    </row>
-    <row r="388" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K387" s="42" t="s">
+        <v>812</v>
+      </c>
+      <c r="L387" s="44" t="str">
+        <f t="shared" si="6"/>
+        <v>*P0074*</v>
+      </c>
+    </row>
+    <row r="388" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A388" s="6"/>
       <c r="B388" s="6"/>
       <c r="C388" s="38" t="s">
@@ -11421,8 +15330,15 @@
       <c r="J388" s="28">
         <v>250</v>
       </c>
-    </row>
-    <row r="389" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K388" s="42" t="s">
+        <v>813</v>
+      </c>
+      <c r="L388" s="44" t="str">
+        <f t="shared" si="6"/>
+        <v>*P0068*</v>
+      </c>
+    </row>
+    <row r="389" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A389" s="6"/>
       <c r="B389" s="6"/>
       <c r="C389" s="38" t="s">
@@ -11447,8 +15363,15 @@
       <c r="J389" s="28">
         <v>250</v>
       </c>
-    </row>
-    <row r="390" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K389" s="42" t="s">
+        <v>814</v>
+      </c>
+      <c r="L389" s="44" t="str">
+        <f t="shared" si="6"/>
+        <v>*P0072*</v>
+      </c>
+    </row>
+    <row r="390" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A390" s="6"/>
       <c r="B390" s="6"/>
       <c r="C390" s="38" t="s">
@@ -11473,8 +15396,15 @@
       <c r="J390" s="28">
         <v>250</v>
       </c>
-    </row>
-    <row r="391" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K390" s="42" t="s">
+        <v>815</v>
+      </c>
+      <c r="L390" s="44" t="str">
+        <f t="shared" si="6"/>
+        <v>*P0071*</v>
+      </c>
+    </row>
+    <row r="391" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A391" s="6"/>
       <c r="B391" s="6"/>
       <c r="C391" s="39" t="s">
@@ -11499,8 +15429,15 @@
       <c r="J391" s="28">
         <v>250</v>
       </c>
-    </row>
-    <row r="392" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K391" s="42" t="s">
+        <v>816</v>
+      </c>
+      <c r="L391" s="44" t="str">
+        <f t="shared" si="6"/>
+        <v>*P0067*</v>
+      </c>
+    </row>
+    <row r="392" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A392" s="6"/>
       <c r="B392" s="6"/>
       <c r="C392" s="39" t="s">
@@ -11525,8 +15462,15 @@
       <c r="J392" s="28">
         <v>250</v>
       </c>
-    </row>
-    <row r="393" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K392" s="42" t="s">
+        <v>817</v>
+      </c>
+      <c r="L392" s="44" t="str">
+        <f t="shared" si="6"/>
+        <v>*P0070*</v>
+      </c>
+    </row>
+    <row r="393" spans="1:12" ht="78" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A393" s="6"/>
       <c r="B393" s="6"/>
       <c r="C393" s="39" t="s">
@@ -11547,8 +15491,16 @@
       <c r="J393" s="28">
         <v>30</v>
       </c>
+      <c r="K393" s="42" t="s">
+        <v>818</v>
+      </c>
+      <c r="L393" s="44" t="str">
+        <f t="shared" si="6"/>
+        <v>*P0046*</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>